--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>42804</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.291000008583069</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.289000004529953</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>250</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>795</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.293999999761581</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.293999999761581</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.293999999761581</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.293999999761581</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>14316</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.293000012636185</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.287000000476837</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.287000000476837</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.293000012636185</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -62796,19 +62796,19 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="C2715" t="n">
         <v>0.284999996423721</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.284999996423721</v>
+        <v>0.28099998831749</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.284999996423721</v>
+        <v>0.28099998831749</v>
       </c>
       <c r="F2715" t="n">
         <v>0.284999996423721</v>
@@ -62819,13 +62819,13 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>34815</v>
+        <v>0</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.28999999165535</v>
+        <v>0.284999996423721</v>
       </c>
       <c r="D2716" t="n">
         <v>0.284999996423721</v>
@@ -62834,7 +62834,7 @@
         <v>0.284999996423721</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.28999999165535</v>
+        <v>0.284999996423721</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,19 +62842,19 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>10150</v>
+        <v>34815</v>
       </c>
       <c r="C2717" t="n">
         <v>0.28999999165535</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.28999999165535</v>
+        <v>0.284999996423721</v>
       </c>
       <c r="E2717" t="n">
-        <v>0.28999999165535</v>
+        <v>0.284999996423721</v>
       </c>
       <c r="F2717" t="n">
         <v>0.28999999165535</v>
@@ -62865,13 +62865,13 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>40500</v>
+        <v>10150</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.291999995708466</v>
+        <v>0.28999999165535</v>
       </c>
       <c r="D2718" t="n">
         <v>0.28999999165535</v>
@@ -62888,16 +62888,16 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>42804</v>
+        <v>40500</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.291000008583069</v>
+        <v>0.291999995708466</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.289000004529953</v>
+        <v>0.28999999165535</v>
       </c>
       <c r="E2719" t="n">
         <v>0.28999999165535</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>250</v>
+        <v>42804</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.284999996423721</v>
+        <v>0.291000008583069</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.284999996423721</v>
+        <v>0.289000004529953</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.284999996423721</v>
+        <v>0.28999999165535</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.284999996423721</v>
+        <v>0.28999999165535</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>795</v>
+        <v>250</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.293999999761581</v>
+        <v>0.284999996423721</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.293999999761581</v>
+        <v>0.284999996423721</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.293999999761581</v>
+        <v>0.284999996423721</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.293999999761581</v>
+        <v>0.284999996423721</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>14316</v>
+        <v>795</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.293000012636185</v>
+        <v>0.293999999761581</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.287000000476837</v>
+        <v>0.293999999761581</v>
       </c>
       <c r="E2722" t="n">
-        <v>0.287000000476837</v>
+        <v>0.293999999761581</v>
       </c>
       <c r="F2722" t="n">
-        <v>0.293000012636185</v>
+        <v>0.293999999761581</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>20765</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.28600001335144</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.28600001335144</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.28600001335144</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.28600001335144</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -447,7 +447,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.939237952232361</v>
+        <v>0.939238011837006</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.04030704498291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926879405975342</v>
+        <v>0.926879465579987</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.01058399677277</v>
       </c>
       <c r="G8" t="n">
-        <v>0.900397121906281</v>
+        <v>0.900397181510925</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.02049195766449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.90922486782074</v>
+        <v>0.909224808216095</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.998695015907288</v>
       </c>
       <c r="G11" t="n">
-        <v>0.889804482460022</v>
+        <v>0.889804422855377</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G15" t="n">
-        <v>0.882742643356323</v>
+        <v>0.882742702960968</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.951138019561768</v>
       </c>
       <c r="G18" t="n">
-        <v>0.847432732582092</v>
+        <v>0.847432792186737</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.970457971096039</v>
       </c>
       <c r="G19" t="n">
-        <v>0.864646196365356</v>
+        <v>0.864646255970001</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>0.968972027301788</v>
       </c>
       <c r="G20" t="n">
-        <v>0.86332231760025</v>
+        <v>0.863322257995605</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.790633022785187</v>
       </c>
       <c r="G31" t="n">
-        <v>0.704428136348724</v>
+        <v>0.70442807674408</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>0.910516023635864</v>
       </c>
       <c r="G41" t="n">
-        <v>0.811239838600159</v>
+        <v>0.811239898204803</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.965503990650177</v>
       </c>
       <c r="G43" t="n">
-        <v>0.860232353210449</v>
+        <v>0.860232412815094</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>0.946183979511261</v>
       </c>
       <c r="G47" t="n">
-        <v>0.843018889427185</v>
+        <v>0.84301882982254</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.924881994724274</v>
       </c>
       <c r="G50" t="n">
-        <v>0.824039459228516</v>
+        <v>0.82403951883316</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.920423984527588</v>
       </c>
       <c r="G51" t="n">
-        <v>0.820067584514618</v>
+        <v>0.820067524909973</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.935781002044678</v>
       </c>
       <c r="G60" t="n">
-        <v>0.833750188350677</v>
+        <v>0.833750128746033</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.95856899023056</v>
       </c>
       <c r="G63" t="n">
-        <v>0.854053556919098</v>
+        <v>0.854053497314453</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.952624022960663</v>
       </c>
       <c r="G66" t="n">
-        <v>0.848756670951843</v>
+        <v>0.848756730556488</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.971943974494934</v>
       </c>
       <c r="G67" t="n">
-        <v>0.865970134735107</v>
+        <v>0.865970194339752</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.957081973552704</v>
       </c>
       <c r="G70" t="n">
-        <v>0.852728605270386</v>
+        <v>0.852728664875031</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.979870021343231</v>
       </c>
       <c r="G71" t="n">
-        <v>0.873032033443451</v>
+        <v>0.873031973838806</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.01652801036835</v>
       </c>
       <c r="G73" t="n">
-        <v>0.905693054199219</v>
+        <v>0.905693113803864</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.05814099311829</v>
       </c>
       <c r="G74" t="n">
-        <v>0.94276887178421</v>
+        <v>0.942768931388855</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G76" t="n">
-        <v>0.986905634403229</v>
+        <v>0.986905694007874</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G77" t="n">
-        <v>0.997498393058777</v>
+        <v>0.997498333454132</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.18595004081726</v>
       </c>
       <c r="G78" t="n">
-        <v>1.05664265155792</v>
+        <v>1.05664253234863</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.1274950504303</v>
       </c>
       <c r="G81" t="n">
-        <v>1.0045610666275</v>
+        <v>1.00456094741821</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.19982099533081</v>
       </c>
       <c r="G84" t="n">
-        <v>1.06900107860565</v>
+        <v>1.06900119781494</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G85" t="n">
-        <v>1.08930361270905</v>
+        <v>1.08930349349976</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.16018998622894</v>
       </c>
       <c r="G86" t="n">
-        <v>1.03369116783142</v>
+        <v>1.03369128704071</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.13641202449799</v>
       </c>
       <c r="G89" t="n">
-        <v>1.01250576972961</v>
+        <v>1.0125058889389</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G92" t="n">
-        <v>0.986905634403229</v>
+        <v>0.986905694007874</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.10569798946381</v>
       </c>
       <c r="G93" t="n">
-        <v>0.985140681266785</v>
+        <v>0.98514062166214</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G94" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134019851685</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.07795596122742</v>
       </c>
       <c r="G95" t="n">
-        <v>0.960423350334167</v>
+        <v>0.960423409938812</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G99" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134019851685</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G100" t="n">
-        <v>0.944533944129944</v>
+        <v>0.944533884525299</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971015989780426</v>
+        <v>0.971016108989716</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G102" t="n">
-        <v>0.997498393058777</v>
+        <v>0.997498333454132</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.11758697032928</v>
       </c>
       <c r="G104" t="n">
-        <v>0.995733201503754</v>
+        <v>0.995733320713043</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.12947595119476</v>
       </c>
       <c r="G111" t="n">
-        <v>1.05007898807526</v>
+        <v>1.05007886886597</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G113" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G114" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G116" t="n">
-        <v>0.953360855579376</v>
+        <v>0.953360915184021</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G117" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G120" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G122" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.989777982234955</v>
       </c>
       <c r="G124" t="n">
-        <v>0.920201063156128</v>
+        <v>0.920201122760773</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G139" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G143" t="n">
-        <v>0.95244038105011</v>
+        <v>0.952440440654755</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G144" t="n">
-        <v>0.944150328636169</v>
+        <v>0.944150269031525</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G158" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G159" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.03931605815887</v>
       </c>
       <c r="G162" t="n">
-        <v>0.96625691652298</v>
+        <v>0.966256856918335</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G164" t="n">
-        <v>0.959809303283691</v>
+        <v>0.959809362888336</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G165" t="n">
-        <v>0.95244038105011</v>
+        <v>0.952440440654755</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G168" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G172" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G179" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.09876203536987</v>
       </c>
       <c r="G181" t="n">
-        <v>1.02152407169342</v>
+        <v>1.02152395248413</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G190" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G192" t="n">
-        <v>0.986521542072296</v>
+        <v>0.986521601676941</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G193" t="n">
-        <v>0.971783936023712</v>
+        <v>0.971783995628357</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G194" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G200" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G202" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G203" t="n">
-        <v>0.964415073394775</v>
+        <v>0.96441513299942</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G204" t="n">
-        <v>0.964415073394775</v>
+        <v>0.96441513299942</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.04129803180695</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968099534511566</v>
+        <v>0.968099474906921</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G206" t="n">
-        <v>0.971783936023712</v>
+        <v>0.971783995628357</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.05318701267242</v>
       </c>
       <c r="G207" t="n">
-        <v>0.979152798652649</v>
+        <v>0.979152739048004</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G208" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G209" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G210" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G211" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G212" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G213" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G215" t="n">
-        <v>0.980074048042297</v>
+        <v>0.980074107646942</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G216" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G217" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G218" t="n">
-        <v>0.969019889831543</v>
+        <v>0.969019830226898</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G219" t="n">
-        <v>0.969019889831543</v>
+        <v>0.969019830226898</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.01850998401642</v>
       </c>
       <c r="G223" t="n">
-        <v>0.946913361549377</v>
+        <v>0.946913421154022</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G225" t="n">
-        <v>0.944150328636169</v>
+        <v>0.944150269031525</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.01256501674652</v>
       </c>
       <c r="G227" t="n">
-        <v>0.941386342048645</v>
+        <v>0.941386282444</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G228" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G229" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G230" t="n">
-        <v>0.921122431755066</v>
+        <v>0.921122491359711</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G231" t="n">
-        <v>0.908226490020752</v>
+        <v>0.908226549625397</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G232" t="n">
-        <v>0.908226490020752</v>
+        <v>0.908226549625397</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G234" t="n">
-        <v>0.921122431755066</v>
+        <v>0.921122491359711</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G241" t="n">
-        <v>0.953360855579376</v>
+        <v>0.953360915184021</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G247" t="n">
-        <v>0.959809303283691</v>
+        <v>0.959809362888336</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G249" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G250" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G251" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G252" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G253" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G256" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G260" t="n">
-        <v>0.986521542072296</v>
+        <v>0.986521601676941</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G264" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.09182703495026</v>
       </c>
       <c r="G270" t="n">
-        <v>1.01507663726807</v>
+        <v>1.01507651805878</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.1086699962616</v>
       </c>
       <c r="G273" t="n">
-        <v>1.03073561191559</v>
+        <v>1.0307354927063</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G276" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G279" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G282" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G283" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G284" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G285" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G286" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.06210398674011</v>
       </c>
       <c r="G287" t="n">
-        <v>0.987442910671234</v>
+        <v>0.987442851066589</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.0650759935379</v>
       </c>
       <c r="G288" t="n">
-        <v>0.990205943584442</v>
+        <v>0.990206062793732</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G289" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.05615901947021</v>
       </c>
       <c r="G290" t="n">
-        <v>0.981915891170502</v>
+        <v>0.981915831565857</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G291" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G292" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G293" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G296" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.11263298988342</v>
       </c>
       <c r="G298" t="n">
-        <v>1.03442001342773</v>
+        <v>1.03441989421844</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.21270096302032</v>
       </c>
       <c r="G304" t="n">
-        <v>1.12745356559753</v>
+        <v>1.12745368480682</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.16613495349884</v>
       </c>
       <c r="G307" t="n">
-        <v>1.08416092395782</v>
+        <v>1.08416104316711</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.17802405357361</v>
       </c>
       <c r="G309" t="n">
-        <v>1.09521436691284</v>
+        <v>1.09521424770355</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.1869410276413</v>
       </c>
       <c r="G310" t="n">
-        <v>1.10350453853607</v>
+        <v>1.10350441932678</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G315" t="n">
-        <v>1.13666427135468</v>
+        <v>1.13666415214539</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.21864497661591</v>
       </c>
       <c r="G316" t="n">
-        <v>1.13297986984253</v>
+        <v>1.13297975063324</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G318" t="n">
-        <v>1.13666427135468</v>
+        <v>1.13666415214539</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>1.31673204898834</v>
       </c>
       <c r="G323" t="n">
-        <v>1.22417187690735</v>
+        <v>1.22417175769806</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G327" t="n">
-        <v>1.1799578666687</v>
+        <v>1.17995774745941</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.29889798164368</v>
       </c>
       <c r="G330" t="n">
-        <v>1.2075914144516</v>
+        <v>1.20759129524231</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G331" t="n">
-        <v>1.16521918773651</v>
+        <v>1.16521906852722</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.22954404354095</v>
       </c>
       <c r="G339" t="n">
-        <v>1.14311265945435</v>
+        <v>1.14311277866364</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.19783902168274</v>
       </c>
       <c r="G342" t="n">
-        <v>1.11363649368286</v>
+        <v>1.11363637447357</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.19585800170898</v>
       </c>
       <c r="G343" t="n">
-        <v>1.11179459095001</v>
+        <v>1.1117947101593</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.20378398895264</v>
       </c>
       <c r="G344" t="n">
-        <v>1.11916351318359</v>
+        <v>1.1191633939743</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.22657203674316</v>
       </c>
       <c r="G345" t="n">
-        <v>1.14034962654114</v>
+        <v>1.14034950733185</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G348" t="n">
-        <v>1.16521918773651</v>
+        <v>1.16521906852722</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.31375896930695</v>
       </c>
       <c r="G350" t="n">
-        <v>1.22140777111053</v>
+        <v>1.22140765190125</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.26719295978546</v>
       </c>
       <c r="G353" t="n">
-        <v>1.17811512947083</v>
+        <v>1.17811501026154</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G354" t="n">
-        <v>1.1799578666687</v>
+        <v>1.17995774745941</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.35834395885468</v>
       </c>
       <c r="G360" t="n">
-        <v>1.26285862922668</v>
+        <v>1.2628585100174</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>0.284999996423721</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>12402</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>0.291000008583069</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>0.282000005245209</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>0.282000005245209</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>0.291000008583069</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>0.291000008583069</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.05913197994232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.943651854991913</v>
+        <v>0.943651795387268</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.04030704498291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926879465579987</v>
+        <v>0.926879405975342</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.910106956958771</v>
+        <v>0.910106897354126</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G6" t="n">
-        <v>0.891569495201111</v>
+        <v>0.891569435596466</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.01058399677277</v>
       </c>
       <c r="G8" t="n">
-        <v>0.900397181510925</v>
+        <v>0.900397121906281</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910106956958771</v>
+        <v>0.910106897354126</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.02049195766449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.909224808216095</v>
+        <v>0.90922486782074</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.998695015907288</v>
       </c>
       <c r="G11" t="n">
-        <v>0.889804422855377</v>
+        <v>0.889804482460022</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G16" t="n">
-        <v>0.891569495201111</v>
+        <v>0.891569435596466</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.951138019561768</v>
       </c>
       <c r="G18" t="n">
-        <v>0.847432792186737</v>
+        <v>0.847432732582092</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.970457971096039</v>
       </c>
       <c r="G19" t="n">
-        <v>0.864646255970001</v>
+        <v>0.864646196365356</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.870885014533997</v>
       </c>
       <c r="G26" t="n">
-        <v>0.775929987430573</v>
+        <v>0.775929927825928</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.812430024147034</v>
       </c>
       <c r="G29" t="n">
-        <v>0.723848521709442</v>
+        <v>0.723848462104797</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.76834100484848</v>
       </c>
       <c r="G30" t="n">
-        <v>0.684566617012024</v>
+        <v>0.684566557407379</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.790633022785187</v>
       </c>
       <c r="G31" t="n">
-        <v>0.70442807674408</v>
+        <v>0.704428017139435</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.8332359790802</v>
       </c>
       <c r="G34" t="n">
-        <v>0.742385864257812</v>
+        <v>0.742385923862457</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.837198972702026</v>
       </c>
       <c r="G39" t="n">
-        <v>0.745916783809662</v>
+        <v>0.745916843414307</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G46" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.925378024578094</v>
       </c>
       <c r="G49" t="n">
-        <v>0.82448148727417</v>
+        <v>0.824481427669525</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.920423984527588</v>
       </c>
       <c r="G51" t="n">
-        <v>0.820067524909973</v>
+        <v>0.820067584514618</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.913488984107971</v>
       </c>
       <c r="G52" t="n">
-        <v>0.813888669013977</v>
+        <v>0.813888728618622</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.933304011821747</v>
       </c>
       <c r="G58" t="n">
-        <v>0.831543207168579</v>
+        <v>0.831543266773224</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.933304011821747</v>
       </c>
       <c r="G59" t="n">
-        <v>0.831543207168579</v>
+        <v>0.831543266773224</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.935781002044678</v>
       </c>
       <c r="G60" t="n">
-        <v>0.833750128746033</v>
+        <v>0.833750188350677</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G61" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.95856899023056</v>
       </c>
       <c r="G63" t="n">
-        <v>0.854053497314453</v>
+        <v>0.854053556919098</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G68" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.957081973552704</v>
       </c>
       <c r="G70" t="n">
-        <v>0.852728664875031</v>
+        <v>0.852728605270386</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.979870021343231</v>
       </c>
       <c r="G71" t="n">
-        <v>0.873031973838806</v>
+        <v>0.873032033443451</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.15919899940491</v>
       </c>
       <c r="G80" t="n">
-        <v>1.03280830383301</v>
+        <v>1.03280818462372</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.1274950504303</v>
       </c>
       <c r="G81" t="n">
-        <v>1.00456094741821</v>
+        <v>1.0045610666275</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.16018998622894</v>
       </c>
       <c r="G86" t="n">
-        <v>1.03369128704071</v>
+        <v>1.03369116783142</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G94" t="n">
-        <v>0.970134019851685</v>
+        <v>0.970134079456329</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.09975302219391</v>
       </c>
       <c r="G96" t="n">
-        <v>0.979843854904175</v>
+        <v>0.97984379529953</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G97" t="n">
-        <v>0.981609702110291</v>
+        <v>0.981609761714935</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G98" t="n">
-        <v>0.981609702110291</v>
+        <v>0.981609761714935</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G99" t="n">
-        <v>0.970134019851685</v>
+        <v>0.970134079456329</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971016108989716</v>
+        <v>0.971016049385071</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.11758697032928</v>
       </c>
       <c r="G104" t="n">
-        <v>0.995733320713043</v>
+        <v>0.995733380317688</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.13443005084991</v>
       </c>
       <c r="G106" t="n">
-        <v>1.0107399225235</v>
+        <v>1.01074004173279</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>0.291000008583069</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>6387</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>0.284000009298325</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.284000009298325</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>0.284000009298325</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.05913197994232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.943651795387268</v>
+        <v>0.943651854991913</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.939238011837006</v>
+        <v>0.939237952232361</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G6" t="n">
-        <v>0.891569435596466</v>
+        <v>0.891569495201111</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G15" t="n">
-        <v>0.882742702960968</v>
+        <v>0.882742643356323</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G16" t="n">
-        <v>0.891569435596466</v>
+        <v>0.891569495201111</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>0.968972027301788</v>
       </c>
       <c r="G20" t="n">
-        <v>0.863322257995605</v>
+        <v>0.86332231760025</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.870885014533997</v>
       </c>
       <c r="G26" t="n">
-        <v>0.775929927825928</v>
+        <v>0.775929987430573</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.812430024147034</v>
       </c>
       <c r="G29" t="n">
-        <v>0.723848462104797</v>
+        <v>0.723848521709442</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.76834100484848</v>
       </c>
       <c r="G30" t="n">
-        <v>0.684566557407379</v>
+        <v>0.684566617012024</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.790633022785187</v>
       </c>
       <c r="G31" t="n">
-        <v>0.704428017139435</v>
+        <v>0.704428136348724</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.8332359790802</v>
       </c>
       <c r="G34" t="n">
-        <v>0.742385923862457</v>
+        <v>0.742385864257812</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.837198972702026</v>
       </c>
       <c r="G39" t="n">
-        <v>0.745916843414307</v>
+        <v>0.745916783809662</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>0.910516023635864</v>
       </c>
       <c r="G41" t="n">
-        <v>0.811239898204803</v>
+        <v>0.811239838600159</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.965503990650177</v>
       </c>
       <c r="G43" t="n">
-        <v>0.860232412815094</v>
+        <v>0.860232353210449</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G46" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>0.946183979511261</v>
       </c>
       <c r="G47" t="n">
-        <v>0.84301882982254</v>
+        <v>0.843018889427185</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.925378024578094</v>
       </c>
       <c r="G49" t="n">
-        <v>0.824481427669525</v>
+        <v>0.82448148727417</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.924881994724274</v>
       </c>
       <c r="G50" t="n">
-        <v>0.82403951883316</v>
+        <v>0.824039459228516</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.913488984107971</v>
       </c>
       <c r="G52" t="n">
-        <v>0.813888728618622</v>
+        <v>0.813888669013977</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.933304011821747</v>
       </c>
       <c r="G58" t="n">
-        <v>0.831543266773224</v>
+        <v>0.831543207168579</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.933304011821747</v>
       </c>
       <c r="G59" t="n">
-        <v>0.831543266773224</v>
+        <v>0.831543207168579</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G61" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.952624022960663</v>
       </c>
       <c r="G66" t="n">
-        <v>0.848756730556488</v>
+        <v>0.848756670951843</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.971943974494934</v>
       </c>
       <c r="G67" t="n">
-        <v>0.865970194339752</v>
+        <v>0.865970134735107</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G68" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.01652801036835</v>
       </c>
       <c r="G73" t="n">
-        <v>0.905693113803864</v>
+        <v>0.905693054199219</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.05814099311829</v>
       </c>
       <c r="G74" t="n">
-        <v>0.942768931388855</v>
+        <v>0.94276887178421</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G76" t="n">
-        <v>0.986905694007874</v>
+        <v>0.986905634403229</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G77" t="n">
-        <v>0.997498333454132</v>
+        <v>0.997498393058777</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.18595004081726</v>
       </c>
       <c r="G78" t="n">
-        <v>1.05664253234863</v>
+        <v>1.05664265155792</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.15919899940491</v>
       </c>
       <c r="G80" t="n">
-        <v>1.03280818462372</v>
+        <v>1.03280830383301</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.19982099533081</v>
       </c>
       <c r="G84" t="n">
-        <v>1.06900119781494</v>
+        <v>1.06900107860565</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G85" t="n">
-        <v>1.08930349349976</v>
+        <v>1.08930361270905</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.13641202449799</v>
       </c>
       <c r="G89" t="n">
-        <v>1.0125058889389</v>
+        <v>1.01250576972961</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G92" t="n">
-        <v>0.986905694007874</v>
+        <v>0.986905634403229</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.10569798946381</v>
       </c>
       <c r="G93" t="n">
-        <v>0.98514062166214</v>
+        <v>0.985140681266785</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.07795596122742</v>
       </c>
       <c r="G95" t="n">
-        <v>0.960423409938812</v>
+        <v>0.960423350334167</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.09975302219391</v>
       </c>
       <c r="G96" t="n">
-        <v>0.97984379529953</v>
+        <v>0.979843854904175</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G97" t="n">
-        <v>0.981609761714935</v>
+        <v>0.981609702110291</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G98" t="n">
-        <v>0.981609761714935</v>
+        <v>0.981609702110291</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G100" t="n">
-        <v>0.944533884525299</v>
+        <v>0.944533944129944</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971016049385071</v>
+        <v>0.971015989780426</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G102" t="n">
-        <v>0.997498333454132</v>
+        <v>0.997498393058777</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.11758697032928</v>
       </c>
       <c r="G104" t="n">
-        <v>0.995733380317688</v>
+        <v>0.995733201503754</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.13443005084991</v>
       </c>
       <c r="G106" t="n">
-        <v>1.01074004173279</v>
+        <v>1.0107399225235</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.12947595119476</v>
       </c>
       <c r="G111" t="n">
-        <v>1.05007886886597</v>
+        <v>1.05007898807526</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G113" t="n">
-        <v>0.99296909570694</v>
+        <v>0.992969155311584</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G114" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G116" t="n">
-        <v>0.953360915184021</v>
+        <v>0.953360855579376</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G117" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G120" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G122" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.989777982234955</v>
       </c>
       <c r="G124" t="n">
-        <v>0.920201122760773</v>
+        <v>0.920201063156128</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G139" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G143" t="n">
-        <v>0.952440440654755</v>
+        <v>0.95244038105011</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G144" t="n">
-        <v>0.944150269031525</v>
+        <v>0.944150328636169</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G158" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G159" t="n">
-        <v>0.993890345096588</v>
+        <v>0.993890404701233</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.03931605815887</v>
       </c>
       <c r="G162" t="n">
-        <v>0.966256856918335</v>
+        <v>0.96625691652298</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G164" t="n">
-        <v>0.959809362888336</v>
+        <v>0.959809303283691</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G165" t="n">
-        <v>0.952440440654755</v>
+        <v>0.95244038105011</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G168" t="n">
-        <v>0.993890345096588</v>
+        <v>0.993890404701233</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G172" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G179" t="n">
-        <v>0.996654331684113</v>
+        <v>0.996654391288757</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.09876203536987</v>
       </c>
       <c r="G181" t="n">
-        <v>1.02152395248413</v>
+        <v>1.02152407169342</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G190" t="n">
-        <v>0.994811713695526</v>
+        <v>0.994811773300171</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G192" t="n">
-        <v>0.986521601676941</v>
+        <v>0.986521542072296</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G193" t="n">
-        <v>0.971783995628357</v>
+        <v>0.971783936023712</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G194" t="n">
-        <v>0.993890345096588</v>
+        <v>0.993890404701233</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G200" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G202" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G203" t="n">
-        <v>0.96441513299942</v>
+        <v>0.964415073394775</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G204" t="n">
-        <v>0.96441513299942</v>
+        <v>0.964415073394775</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.04129803180695</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968099474906921</v>
+        <v>0.968099534511566</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G206" t="n">
-        <v>0.971783995628357</v>
+        <v>0.971783936023712</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.05318701267242</v>
       </c>
       <c r="G207" t="n">
-        <v>0.979152739048004</v>
+        <v>0.979152798652649</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G208" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G209" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G210" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G211" t="n">
-        <v>0.99296909570694</v>
+        <v>0.992969155311584</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G212" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G213" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G215" t="n">
-        <v>0.980074107646942</v>
+        <v>0.980074048042297</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G216" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G217" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G218" t="n">
-        <v>0.969019830226898</v>
+        <v>0.969019889831543</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G219" t="n">
-        <v>0.969019830226898</v>
+        <v>0.969019889831543</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.01850998401642</v>
       </c>
       <c r="G223" t="n">
-        <v>0.946913421154022</v>
+        <v>0.946913361549377</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G225" t="n">
-        <v>0.944150269031525</v>
+        <v>0.944150328636169</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.01256501674652</v>
       </c>
       <c r="G227" t="n">
-        <v>0.941386282444</v>
+        <v>0.941386342048645</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G228" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G229" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G230" t="n">
-        <v>0.921122491359711</v>
+        <v>0.921122431755066</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G231" t="n">
-        <v>0.908226549625397</v>
+        <v>0.908226490020752</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G232" t="n">
-        <v>0.908226549625397</v>
+        <v>0.908226490020752</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G234" t="n">
-        <v>0.921122491359711</v>
+        <v>0.921122431755066</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G241" t="n">
-        <v>0.953360915184021</v>
+        <v>0.953360855579376</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G247" t="n">
-        <v>0.959809362888336</v>
+        <v>0.959809303283691</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G249" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G250" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G251" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G252" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G253" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G256" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G260" t="n">
-        <v>0.986521601676941</v>
+        <v>0.986521542072296</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G264" t="n">
-        <v>0.994811713695526</v>
+        <v>0.994811773300171</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.09182703495026</v>
       </c>
       <c r="G270" t="n">
-        <v>1.01507651805878</v>
+        <v>1.01507663726807</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.1086699962616</v>
       </c>
       <c r="G273" t="n">
-        <v>1.0307354927063</v>
+        <v>1.03073561191559</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G276" t="n">
-        <v>0.996654331684113</v>
+        <v>0.996654391288757</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G279" t="n">
-        <v>0.996654331684113</v>
+        <v>0.996654391288757</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G282" t="n">
-        <v>0.994811713695526</v>
+        <v>0.994811773300171</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G283" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G284" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G285" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G286" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.06210398674011</v>
       </c>
       <c r="G287" t="n">
-        <v>0.987442851066589</v>
+        <v>0.987442910671234</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.0650759935379</v>
       </c>
       <c r="G288" t="n">
-        <v>0.990206062793732</v>
+        <v>0.990205943584442</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G289" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.05615901947021</v>
       </c>
       <c r="G290" t="n">
-        <v>0.981915831565857</v>
+        <v>0.981915891170502</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G291" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G292" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G293" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G296" t="n">
-        <v>0.99296909570694</v>
+        <v>0.992969155311584</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.11263298988342</v>
       </c>
       <c r="G298" t="n">
-        <v>1.03441989421844</v>
+        <v>1.03442001342773</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.21270096302032</v>
       </c>
       <c r="G304" t="n">
-        <v>1.12745368480682</v>
+        <v>1.12745356559753</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.16613495349884</v>
       </c>
       <c r="G307" t="n">
-        <v>1.08416104316711</v>
+        <v>1.08416092395782</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.17802405357361</v>
       </c>
       <c r="G309" t="n">
-        <v>1.09521424770355</v>
+        <v>1.09521436691284</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.1869410276413</v>
       </c>
       <c r="G310" t="n">
-        <v>1.10350441932678</v>
+        <v>1.10350453853607</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G315" t="n">
-        <v>1.13666415214539</v>
+        <v>1.13666427135468</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.21864497661591</v>
       </c>
       <c r="G316" t="n">
-        <v>1.13297975063324</v>
+        <v>1.13297986984253</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G318" t="n">
-        <v>1.13666415214539</v>
+        <v>1.13666427135468</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>1.31673204898834</v>
       </c>
       <c r="G323" t="n">
-        <v>1.22417175769806</v>
+        <v>1.22417187690735</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G327" t="n">
-        <v>1.17995774745941</v>
+        <v>1.1799578666687</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.29889798164368</v>
       </c>
       <c r="G330" t="n">
-        <v>1.20759129524231</v>
+        <v>1.2075914144516</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G331" t="n">
-        <v>1.16521906852722</v>
+        <v>1.16521918773651</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.22954404354095</v>
       </c>
       <c r="G339" t="n">
-        <v>1.14311277866364</v>
+        <v>1.14311265945435</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.19783902168274</v>
       </c>
       <c r="G342" t="n">
-        <v>1.11363637447357</v>
+        <v>1.11363649368286</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.19585800170898</v>
       </c>
       <c r="G343" t="n">
-        <v>1.1117947101593</v>
+        <v>1.11179459095001</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.20378398895264</v>
       </c>
       <c r="G344" t="n">
-        <v>1.1191633939743</v>
+        <v>1.11916351318359</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.22657203674316</v>
       </c>
       <c r="G345" t="n">
-        <v>1.14034950733185</v>
+        <v>1.14034962654114</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G348" t="n">
-        <v>1.16521906852722</v>
+        <v>1.16521918773651</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.31375896930695</v>
       </c>
       <c r="G350" t="n">
-        <v>1.22140765190125</v>
+        <v>1.22140777111053</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.26719295978546</v>
       </c>
       <c r="G353" t="n">
-        <v>1.17811501026154</v>
+        <v>1.17811512947083</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G354" t="n">
-        <v>1.17995774745941</v>
+        <v>1.1799578666687</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.35834395885468</v>
       </c>
       <c r="G360" t="n">
-        <v>1.2628585100174</v>
+        <v>1.26285862922668</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -71259,7 +71259,7 @@
         <v>6387</v>
       </c>
       <c r="C2727" t="n">
-        <v>0.284000009298325</v>
+        <v>0.284999996423721</v>
       </c>
       <c r="D2727" t="n">
         <v>0.284000009298325</v>
@@ -71274,6 +71274,32 @@
         <v>0.284999996423721</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>3472</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -71303,6 +71303,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>0.291000008583069</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>0.291000008583069</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>0.291000008583069</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="H2729" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.05913197994232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.943651854991913</v>
+        <v>0.943651914596558</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.966989994049072</v>
       </c>
       <c r="G17" t="n">
-        <v>0.861556351184845</v>
+        <v>0.8615562915802</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.970457971096039</v>
       </c>
       <c r="G19" t="n">
-        <v>0.864646255970001</v>
+        <v>0.864646196365356</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>0.968972027301788</v>
       </c>
       <c r="G20" t="n">
-        <v>0.863322257995605</v>
+        <v>0.86332231760025</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G22" t="n">
-        <v>0.85625958442688</v>
+        <v>0.856259524822235</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.921414971351624</v>
       </c>
       <c r="G23" t="n">
-        <v>0.820950508117676</v>
+        <v>0.820950448513031</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.824814975261688</v>
       </c>
       <c r="G28" t="n">
-        <v>0.734883069992065</v>
+        <v>0.734883010387421</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.812430024147034</v>
       </c>
       <c r="G29" t="n">
-        <v>0.723848521709442</v>
+        <v>0.723848462104797</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.8332359790802</v>
       </c>
       <c r="G34" t="n">
-        <v>0.742385864257812</v>
+        <v>0.742385923862457</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>0.822833001613617</v>
       </c>
       <c r="G38" t="n">
-        <v>0.733117163181305</v>
+        <v>0.73311722278595</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.931321978569031</v>
       </c>
       <c r="G42" t="n">
-        <v>0.829777359962463</v>
+        <v>0.829777300357819</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.965503990650177</v>
       </c>
       <c r="G43" t="n">
-        <v>0.860232412815094</v>
+        <v>0.860232353210449</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G46" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>0.946183979511261</v>
       </c>
       <c r="G47" t="n">
-        <v>0.84301882982254</v>
+        <v>0.843018889427185</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G48" t="n">
-        <v>0.85625958442688</v>
+        <v>0.856259524822235</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.925378024578094</v>
       </c>
       <c r="G49" t="n">
-        <v>0.82448148727417</v>
+        <v>0.824481427669525</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>0.9288449883461</v>
       </c>
       <c r="G56" t="n">
-        <v>0.827570378780365</v>
+        <v>0.82757043838501</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.931321978569031</v>
       </c>
       <c r="G57" t="n">
-        <v>0.829777359962463</v>
+        <v>0.829777300357819</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G61" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>0.955101013183594</v>
       </c>
       <c r="G62" t="n">
-        <v>0.850963652133942</v>
+        <v>0.850963592529297</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G65" t="n">
-        <v>0.85625958442688</v>
+        <v>0.856259524822235</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.952624022960663</v>
       </c>
       <c r="G66" t="n">
-        <v>0.848756730556488</v>
+        <v>0.848756790161133</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G68" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.94370698928833</v>
       </c>
       <c r="G69" t="n">
-        <v>0.840811967849731</v>
+        <v>0.840811908245087</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.979870021343231</v>
       </c>
       <c r="G71" t="n">
-        <v>0.873031973838806</v>
+        <v>0.873032033443451</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.01652801036835</v>
       </c>
       <c r="G73" t="n">
-        <v>0.905693113803864</v>
+        <v>0.905693054199219</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.0710209608078</v>
       </c>
       <c r="G75" t="n">
-        <v>0.954244554042816</v>
+        <v>0.954244494438171</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G76" t="n">
-        <v>0.986905694007874</v>
+        <v>0.986905574798584</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.1274950504303</v>
       </c>
       <c r="G81" t="n">
-        <v>1.00456094741821</v>
+        <v>1.0045610666275</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.21765494346619</v>
       </c>
       <c r="G82" t="n">
-        <v>1.08489060401917</v>
+        <v>1.08489048480988</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.16018998622894</v>
       </c>
       <c r="G86" t="n">
-        <v>1.03369128704071</v>
+        <v>1.03369116783142</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.13641202449799</v>
       </c>
       <c r="G89" t="n">
-        <v>1.0125058889389</v>
+        <v>1.01250576972961</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G92" t="n">
-        <v>0.986905694007874</v>
+        <v>0.986905574798584</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G94" t="n">
-        <v>0.970134019851685</v>
+        <v>0.970134139060974</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.07795596122742</v>
       </c>
       <c r="G95" t="n">
-        <v>0.960423409938812</v>
+        <v>0.960423350334167</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G99" t="n">
-        <v>0.970134019851685</v>
+        <v>0.970134139060974</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G100" t="n">
-        <v>0.944533884525299</v>
+        <v>0.944534003734589</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.1492919921875</v>
       </c>
       <c r="G105" t="n">
-        <v>1.02398145198822</v>
+        <v>1.02398157119751</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.14037501811981</v>
       </c>
       <c r="G107" t="n">
-        <v>1.01603674888611</v>
+        <v>1.01603662967682</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>0.284000009298325</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>8831</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>0.284000009298325</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>0.282000005245209</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>0.284000009298325</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>0.284000009298325</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>0.284000009298325</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.282000005245209</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.282000005245209</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.282000005245209</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.282000005245209</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.282000005245209</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.282000005245209</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.282000005245209</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>27408</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.282000005245209</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.28099998831749</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.282000005245209</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.282000005245209</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.28099998831749</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>25110</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.284999996423721</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.280000001192093</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.280000001192093</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.280000001192093</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.284999996423721</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>87769</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.280000001192093</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.268999993801117</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.275999993085861</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>6836</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.277999997138977</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.273000001907349</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.277999997138977</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.273000001907349</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.05913197994232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.943651854991913</v>
+        <v>0.943651795387268</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>0.968972027301788</v>
       </c>
       <c r="G20" t="n">
-        <v>0.86332231760025</v>
+        <v>0.863322257995605</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G24" t="n">
-        <v>0.812122821807861</v>
+        <v>0.812122881412506</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.881784021854401</v>
       </c>
       <c r="G25" t="n">
-        <v>0.785640597343445</v>
+        <v>0.78564065694809</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.870885014533997</v>
       </c>
       <c r="G26" t="n">
-        <v>0.775929987430573</v>
+        <v>0.775929927825928</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.812430024147034</v>
       </c>
       <c r="G29" t="n">
-        <v>0.723848521709442</v>
+        <v>0.723848462104797</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.790633022785187</v>
       </c>
       <c r="G31" t="n">
-        <v>0.704428136348724</v>
+        <v>0.70442807674408</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.8332359790802</v>
       </c>
       <c r="G34" t="n">
-        <v>0.742385864257812</v>
+        <v>0.742385923862457</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>0.910516023635864</v>
       </c>
       <c r="G41" t="n">
-        <v>0.811239838600159</v>
+        <v>0.811239898204803</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.947175025939941</v>
       </c>
       <c r="G45" t="n">
-        <v>0.843901872634888</v>
+        <v>0.843901813030243</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G46" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G53" t="n">
-        <v>0.812122821807861</v>
+        <v>0.812122881412506</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G61" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.95856899023056</v>
       </c>
       <c r="G63" t="n">
-        <v>0.854053556919098</v>
+        <v>0.854053497314453</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.952624022960663</v>
       </c>
       <c r="G66" t="n">
-        <v>0.848756670951843</v>
+        <v>0.848756730556488</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G68" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.94370698928833</v>
       </c>
       <c r="G69" t="n">
-        <v>0.840811967849731</v>
+        <v>0.840811908245087</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.0710209608078</v>
       </c>
       <c r="G75" t="n">
-        <v>0.954244554042816</v>
+        <v>0.954244613647461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G76" t="n">
-        <v>0.986905634403229</v>
+        <v>0.986905694007874</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G77" t="n">
-        <v>0.997498393058777</v>
+        <v>0.997498333454132</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.18595004081726</v>
       </c>
       <c r="G78" t="n">
-        <v>1.05664265155792</v>
+        <v>1.05664253234863</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.19982099533081</v>
       </c>
       <c r="G84" t="n">
-        <v>1.06900107860565</v>
+        <v>1.06900119781494</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.13641202449799</v>
       </c>
       <c r="G89" t="n">
-        <v>1.01250576972961</v>
+        <v>1.0125058889389</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G92" t="n">
-        <v>0.986905634403229</v>
+        <v>0.986905694007874</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.10569798946381</v>
       </c>
       <c r="G93" t="n">
-        <v>0.985140681266785</v>
+        <v>0.98514062166214</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.07795596122742</v>
       </c>
       <c r="G95" t="n">
-        <v>0.960423350334167</v>
+        <v>0.960423409938812</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.09975302219391</v>
       </c>
       <c r="G96" t="n">
-        <v>0.979843854904175</v>
+        <v>0.97984379529953</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G97" t="n">
-        <v>0.981609702110291</v>
+        <v>0.981609761714935</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G98" t="n">
-        <v>0.981609702110291</v>
+        <v>0.981609761714935</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971015989780426</v>
+        <v>0.971016049385071</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G102" t="n">
-        <v>0.997498393058777</v>
+        <v>0.997498333454132</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.12947595119476</v>
       </c>
       <c r="G103" t="n">
-        <v>1.0063259601593</v>
+        <v>1.00632607936859</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.11758697032928</v>
       </c>
       <c r="G104" t="n">
-        <v>0.995733201503754</v>
+        <v>0.995733261108398</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.13443005084991</v>
       </c>
       <c r="G106" t="n">
-        <v>1.0107399225235</v>
+        <v>1.01074004173279</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.16613495349884</v>
       </c>
       <c r="G108" t="n">
-        <v>1.03898799419403</v>
+        <v>1.03898787498474</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>0.264999985694885</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>16958</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.268999993801117</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.05913197994232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.943651795387268</v>
+        <v>0.943651854991913</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.939237952232361</v>
+        <v>0.939238011837006</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.04030704498291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926879405975342</v>
+        <v>0.926879465579987</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.01058399677277</v>
       </c>
       <c r="G8" t="n">
-        <v>0.900397121906281</v>
+        <v>0.900397181510925</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.02049195766449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.90922486782074</v>
+        <v>0.909224808216095</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.998695015907288</v>
       </c>
       <c r="G11" t="n">
-        <v>0.889804482460022</v>
+        <v>0.889804422855377</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G15" t="n">
-        <v>0.882742643356323</v>
+        <v>0.882742702960968</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.951138019561768</v>
       </c>
       <c r="G18" t="n">
-        <v>0.847432732582092</v>
+        <v>0.847432792186737</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.970457971096039</v>
       </c>
       <c r="G19" t="n">
-        <v>0.864646196365356</v>
+        <v>0.864646255970001</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G24" t="n">
-        <v>0.812122881412506</v>
+        <v>0.812122821807861</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.881784021854401</v>
       </c>
       <c r="G25" t="n">
-        <v>0.78564065694809</v>
+        <v>0.785640597343445</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.870885014533997</v>
       </c>
       <c r="G26" t="n">
-        <v>0.775929927825928</v>
+        <v>0.775929987430573</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.812430024147034</v>
       </c>
       <c r="G29" t="n">
-        <v>0.723848462104797</v>
+        <v>0.723848521709442</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.8332359790802</v>
       </c>
       <c r="G34" t="n">
-        <v>0.742385923862457</v>
+        <v>0.742385864257812</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.965503990650177</v>
       </c>
       <c r="G43" t="n">
-        <v>0.860232353210449</v>
+        <v>0.860232412815094</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.947175025939941</v>
       </c>
       <c r="G45" t="n">
-        <v>0.843901813030243</v>
+        <v>0.843901872634888</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G46" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>0.946183979511261</v>
       </c>
       <c r="G47" t="n">
-        <v>0.843018889427185</v>
+        <v>0.84301882982254</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.924881994724274</v>
       </c>
       <c r="G50" t="n">
-        <v>0.824039459228516</v>
+        <v>0.82403951883316</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.920423984527588</v>
       </c>
       <c r="G51" t="n">
-        <v>0.820067584514618</v>
+        <v>0.820067524909973</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G53" t="n">
-        <v>0.812122881412506</v>
+        <v>0.812122821807861</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.935781002044678</v>
       </c>
       <c r="G60" t="n">
-        <v>0.833750188350677</v>
+        <v>0.833750128746033</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G61" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.971943974494934</v>
       </c>
       <c r="G67" t="n">
-        <v>0.865970134735107</v>
+        <v>0.865970194339752</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G68" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.94370698928833</v>
       </c>
       <c r="G69" t="n">
-        <v>0.840811908245087</v>
+        <v>0.840811967849731</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.957081973552704</v>
       </c>
       <c r="G70" t="n">
-        <v>0.852728605270386</v>
+        <v>0.852728664875031</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.979870021343231</v>
       </c>
       <c r="G71" t="n">
-        <v>0.873032033443451</v>
+        <v>0.873031973838806</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.01652801036835</v>
       </c>
       <c r="G73" t="n">
-        <v>0.905693054199219</v>
+        <v>0.905693113803864</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.05814099311829</v>
       </c>
       <c r="G74" t="n">
-        <v>0.94276887178421</v>
+        <v>0.942768931388855</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.0710209608078</v>
       </c>
       <c r="G75" t="n">
-        <v>0.954244613647461</v>
+        <v>0.954244554042816</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.1274950504303</v>
       </c>
       <c r="G81" t="n">
-        <v>1.0045610666275</v>
+        <v>1.00456094741821</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G85" t="n">
-        <v>1.08930361270905</v>
+        <v>1.08930349349976</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.16018998622894</v>
       </c>
       <c r="G86" t="n">
-        <v>1.03369116783142</v>
+        <v>1.03369128704071</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G94" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134019851685</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.09975302219391</v>
       </c>
       <c r="G96" t="n">
-        <v>0.97984379529953</v>
+        <v>0.979843854904175</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G97" t="n">
-        <v>0.981609761714935</v>
+        <v>0.981609702110291</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G98" t="n">
-        <v>0.981609761714935</v>
+        <v>0.981609702110291</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G99" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134019851685</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G100" t="n">
-        <v>0.944533944129944</v>
+        <v>0.944533884525299</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971016049385071</v>
+        <v>0.971016108989716</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.12947595119476</v>
       </c>
       <c r="G103" t="n">
-        <v>1.00632607936859</v>
+        <v>1.0063259601593</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.11758697032928</v>
       </c>
       <c r="G104" t="n">
-        <v>0.995733261108398</v>
+        <v>0.995733320713043</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.13443005084991</v>
       </c>
       <c r="G106" t="n">
-        <v>1.01074004173279</v>
+        <v>1.0107399225235</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.16613495349884</v>
       </c>
       <c r="G108" t="n">
-        <v>1.03898787498474</v>
+        <v>1.03898799419403</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.12947595119476</v>
       </c>
       <c r="G111" t="n">
-        <v>1.05007898807526</v>
+        <v>1.05007886886597</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G113" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G114" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G116" t="n">
-        <v>0.953360855579376</v>
+        <v>0.953360915184021</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G117" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G120" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G122" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.989777982234955</v>
       </c>
       <c r="G124" t="n">
-        <v>0.920201063156128</v>
+        <v>0.920201122760773</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G139" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G143" t="n">
-        <v>0.95244038105011</v>
+        <v>0.952440440654755</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G144" t="n">
-        <v>0.944150328636169</v>
+        <v>0.944150269031525</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G158" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G159" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.03931605815887</v>
       </c>
       <c r="G162" t="n">
-        <v>0.96625691652298</v>
+        <v>0.966256856918335</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G164" t="n">
-        <v>0.959809303283691</v>
+        <v>0.959809362888336</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G165" t="n">
-        <v>0.95244038105011</v>
+        <v>0.952440440654755</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G168" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G172" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G179" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.09876203536987</v>
       </c>
       <c r="G181" t="n">
-        <v>1.02152407169342</v>
+        <v>1.02152395248413</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G190" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G192" t="n">
-        <v>0.986521542072296</v>
+        <v>0.986521601676941</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G193" t="n">
-        <v>0.971783936023712</v>
+        <v>0.971783995628357</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G194" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G200" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G202" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G203" t="n">
-        <v>0.964415073394775</v>
+        <v>0.96441513299942</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G204" t="n">
-        <v>0.964415073394775</v>
+        <v>0.96441513299942</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.04129803180695</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968099534511566</v>
+        <v>0.968099474906921</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G206" t="n">
-        <v>0.971783936023712</v>
+        <v>0.971783995628357</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.05318701267242</v>
       </c>
       <c r="G207" t="n">
-        <v>0.979152798652649</v>
+        <v>0.979152739048004</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G208" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G209" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G210" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G211" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G212" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G213" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G215" t="n">
-        <v>0.980074048042297</v>
+        <v>0.980074107646942</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G216" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G217" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G218" t="n">
-        <v>0.969019889831543</v>
+        <v>0.969019830226898</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G219" t="n">
-        <v>0.969019889831543</v>
+        <v>0.969019830226898</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.01850998401642</v>
       </c>
       <c r="G223" t="n">
-        <v>0.946913361549377</v>
+        <v>0.946913421154022</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G225" t="n">
-        <v>0.944150328636169</v>
+        <v>0.944150269031525</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.01256501674652</v>
       </c>
       <c r="G227" t="n">
-        <v>0.941386342048645</v>
+        <v>0.941386282444</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G228" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G229" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G230" t="n">
-        <v>0.921122431755066</v>
+        <v>0.921122491359711</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G231" t="n">
-        <v>0.908226490020752</v>
+        <v>0.908226549625397</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G232" t="n">
-        <v>0.908226490020752</v>
+        <v>0.908226549625397</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G234" t="n">
-        <v>0.921122431755066</v>
+        <v>0.921122491359711</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G241" t="n">
-        <v>0.953360855579376</v>
+        <v>0.953360915184021</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G247" t="n">
-        <v>0.959809303283691</v>
+        <v>0.959809362888336</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G249" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G250" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G251" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G252" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G253" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G256" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G260" t="n">
-        <v>0.986521542072296</v>
+        <v>0.986521601676941</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G264" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.09182703495026</v>
       </c>
       <c r="G270" t="n">
-        <v>1.01507663726807</v>
+        <v>1.01507651805878</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.1086699962616</v>
       </c>
       <c r="G273" t="n">
-        <v>1.03073561191559</v>
+        <v>1.0307354927063</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G276" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G279" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G282" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G283" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G284" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G285" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G286" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.06210398674011</v>
       </c>
       <c r="G287" t="n">
-        <v>0.987442910671234</v>
+        <v>0.987442851066589</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.0650759935379</v>
       </c>
       <c r="G288" t="n">
-        <v>0.990205943584442</v>
+        <v>0.990206062793732</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G289" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.05615901947021</v>
       </c>
       <c r="G290" t="n">
-        <v>0.981915891170502</v>
+        <v>0.981915831565857</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G291" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G292" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G293" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G296" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.11263298988342</v>
       </c>
       <c r="G298" t="n">
-        <v>1.03442001342773</v>
+        <v>1.03441989421844</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.21270096302032</v>
       </c>
       <c r="G304" t="n">
-        <v>1.12745356559753</v>
+        <v>1.12745368480682</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.16613495349884</v>
       </c>
       <c r="G307" t="n">
-        <v>1.08416092395782</v>
+        <v>1.08416104316711</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.17802405357361</v>
       </c>
       <c r="G309" t="n">
-        <v>1.09521436691284</v>
+        <v>1.09521424770355</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.1869410276413</v>
       </c>
       <c r="G310" t="n">
-        <v>1.10350453853607</v>
+        <v>1.10350441932678</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G315" t="n">
-        <v>1.13666427135468</v>
+        <v>1.13666415214539</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.21864497661591</v>
       </c>
       <c r="G316" t="n">
-        <v>1.13297986984253</v>
+        <v>1.13297975063324</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G318" t="n">
-        <v>1.13666427135468</v>
+        <v>1.13666415214539</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>1.31673204898834</v>
       </c>
       <c r="G323" t="n">
-        <v>1.22417187690735</v>
+        <v>1.22417175769806</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G327" t="n">
-        <v>1.1799578666687</v>
+        <v>1.17995774745941</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.29889798164368</v>
       </c>
       <c r="G330" t="n">
-        <v>1.2075914144516</v>
+        <v>1.20759129524231</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G331" t="n">
-        <v>1.16521918773651</v>
+        <v>1.16521906852722</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.22954404354095</v>
       </c>
       <c r="G339" t="n">
-        <v>1.14311265945435</v>
+        <v>1.14311277866364</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.19783902168274</v>
       </c>
       <c r="G342" t="n">
-        <v>1.11363649368286</v>
+        <v>1.11363637447357</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.19585800170898</v>
       </c>
       <c r="G343" t="n">
-        <v>1.11179459095001</v>
+        <v>1.1117947101593</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.20378398895264</v>
       </c>
       <c r="G344" t="n">
-        <v>1.11916351318359</v>
+        <v>1.1191633939743</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.22657203674316</v>
       </c>
       <c r="G345" t="n">
-        <v>1.14034962654114</v>
+        <v>1.14034950733185</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G348" t="n">
-        <v>1.16521918773651</v>
+        <v>1.16521906852722</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.31375896930695</v>
       </c>
       <c r="G350" t="n">
-        <v>1.22140777111053</v>
+        <v>1.22140765190125</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.26719295978546</v>
       </c>
       <c r="G353" t="n">
-        <v>1.17811512947083</v>
+        <v>1.17811501026154</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G354" t="n">
-        <v>1.1799578666687</v>
+        <v>1.17995774745941</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.35834395885468</v>
       </c>
       <c r="G360" t="n">
-        <v>1.26285862922668</v>
+        <v>1.2628585100174</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>0.264999985694885</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>3413</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>0.261000007390976</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.05913197994232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.943651795387268</v>
+        <v>0.943651854991913</v>
       </c>
       <c r="H2" t="n">
         <v>13804</v>
@@ -456,7 +456,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.939237952232361</v>
+        <v>0.939238011837006</v>
       </c>
       <c r="H3" t="n">
         <v>17307</v>
@@ -485,7 +485,7 @@
         <v>1.04030704498291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926879405975342</v>
+        <v>0.926879465579987</v>
       </c>
       <c r="H4" t="n">
         <v>6401</v>
@@ -514,7 +514,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H5" t="n">
         <v>44193</v>
@@ -601,7 +601,7 @@
         <v>1.01058399677277</v>
       </c>
       <c r="G8" t="n">
-        <v>0.900397121906281</v>
+        <v>0.900397181510925</v>
       </c>
       <c r="H8" t="n">
         <v>23254</v>
@@ -630,7 +630,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H9" t="n">
         <v>24329</v>
@@ -659,7 +659,7 @@
         <v>1.02049195766449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.90922486782074</v>
+        <v>0.909224808216095</v>
       </c>
       <c r="H10" t="n">
         <v>2966</v>
@@ -688,7 +688,7 @@
         <v>0.998695015907288</v>
       </c>
       <c r="G11" t="n">
-        <v>0.889804482460022</v>
+        <v>0.889804422855377</v>
       </c>
       <c r="H11" t="n">
         <v>63536</v>
@@ -804,7 +804,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G15" t="n">
-        <v>0.882742643356323</v>
+        <v>0.882742702960968</v>
       </c>
       <c r="H15" t="n">
         <v>17895</v>
@@ -891,7 +891,7 @@
         <v>0.951138019561768</v>
       </c>
       <c r="G18" t="n">
-        <v>0.847432732582092</v>
+        <v>0.847432792186737</v>
       </c>
       <c r="H18" t="n">
         <v>8438</v>
@@ -920,7 +920,7 @@
         <v>0.970457971096039</v>
       </c>
       <c r="G19" t="n">
-        <v>0.864646196365356</v>
+        <v>0.864646255970001</v>
       </c>
       <c r="H19" t="n">
         <v>3784</v>
@@ -1065,7 +1065,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G24" t="n">
-        <v>0.812122881412506</v>
+        <v>0.812122821807861</v>
       </c>
       <c r="H24" t="n">
         <v>12656</v>
@@ -1094,7 +1094,7 @@
         <v>0.881784021854401</v>
       </c>
       <c r="G25" t="n">
-        <v>0.78564065694809</v>
+        <v>0.785640597343445</v>
       </c>
       <c r="H25" t="n">
         <v>24991</v>
@@ -1123,7 +1123,7 @@
         <v>0.870885014533997</v>
       </c>
       <c r="G26" t="n">
-        <v>0.775929927825928</v>
+        <v>0.775929987430573</v>
       </c>
       <c r="H26" t="n">
         <v>26138</v>
@@ -1210,7 +1210,7 @@
         <v>0.812430024147034</v>
       </c>
       <c r="G29" t="n">
-        <v>0.723848462104797</v>
+        <v>0.723848521709442</v>
       </c>
       <c r="H29" t="n">
         <v>38859</v>
@@ -1355,7 +1355,7 @@
         <v>0.8332359790802</v>
       </c>
       <c r="G34" t="n">
-        <v>0.742385923862457</v>
+        <v>0.742385864257812</v>
       </c>
       <c r="H34" t="n">
         <v>7451</v>
@@ -1616,7 +1616,7 @@
         <v>0.965503990650177</v>
       </c>
       <c r="G43" t="n">
-        <v>0.860232353210449</v>
+        <v>0.860232412815094</v>
       </c>
       <c r="H43" t="n">
         <v>5234</v>
@@ -1674,7 +1674,7 @@
         <v>0.947175025939941</v>
       </c>
       <c r="G45" t="n">
-        <v>0.843901813030243</v>
+        <v>0.843901872634888</v>
       </c>
       <c r="H45" t="n">
         <v>29503</v>
@@ -1703,7 +1703,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G46" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H46" t="n">
         <v>5147</v>
@@ -1732,7 +1732,7 @@
         <v>0.946183979511261</v>
       </c>
       <c r="G47" t="n">
-        <v>0.843018889427185</v>
+        <v>0.84301882982254</v>
       </c>
       <c r="H47" t="n">
         <v>9568</v>
@@ -1819,7 +1819,7 @@
         <v>0.924881994724274</v>
       </c>
       <c r="G50" t="n">
-        <v>0.824039459228516</v>
+        <v>0.82403951883316</v>
       </c>
       <c r="H50" t="n">
         <v>7700</v>
@@ -1848,7 +1848,7 @@
         <v>0.920423984527588</v>
       </c>
       <c r="G51" t="n">
-        <v>0.820067584514618</v>
+        <v>0.820067524909973</v>
       </c>
       <c r="H51" t="n">
         <v>5213</v>
@@ -1906,7 +1906,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G53" t="n">
-        <v>0.812122881412506</v>
+        <v>0.812122821807861</v>
       </c>
       <c r="H53" t="n">
         <v>5228</v>
@@ -2109,7 +2109,7 @@
         <v>0.935781002044678</v>
       </c>
       <c r="G60" t="n">
-        <v>0.833750188350677</v>
+        <v>0.833750128746033</v>
       </c>
       <c r="H60" t="n">
         <v>4464</v>
@@ -2138,7 +2138,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G61" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H61" t="n">
         <v>25097</v>
@@ -2312,7 +2312,7 @@
         <v>0.971943974494934</v>
       </c>
       <c r="G67" t="n">
-        <v>0.865970134735107</v>
+        <v>0.865970194339752</v>
       </c>
       <c r="H67" t="n">
         <v>10093</v>
@@ -2341,7 +2341,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G68" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H68" t="n">
         <v>18109</v>
@@ -2370,7 +2370,7 @@
         <v>0.94370698928833</v>
       </c>
       <c r="G69" t="n">
-        <v>0.840811908245087</v>
+        <v>0.840811967849731</v>
       </c>
       <c r="H69" t="n">
         <v>14246</v>
@@ -2399,7 +2399,7 @@
         <v>0.957081973552704</v>
       </c>
       <c r="G70" t="n">
-        <v>0.852728605270386</v>
+        <v>0.852728664875031</v>
       </c>
       <c r="H70" t="n">
         <v>20319</v>
@@ -2428,7 +2428,7 @@
         <v>0.979870021343231</v>
       </c>
       <c r="G71" t="n">
-        <v>0.873032033443451</v>
+        <v>0.873031973838806</v>
       </c>
       <c r="H71" t="n">
         <v>1148</v>
@@ -2486,7 +2486,7 @@
         <v>1.01652801036835</v>
       </c>
       <c r="G73" t="n">
-        <v>0.905693054199219</v>
+        <v>0.905693113803864</v>
       </c>
       <c r="H73" t="n">
         <v>22149</v>
@@ -2515,7 +2515,7 @@
         <v>1.05814099311829</v>
       </c>
       <c r="G74" t="n">
-        <v>0.94276887178421</v>
+        <v>0.942768931388855</v>
       </c>
       <c r="H74" t="n">
         <v>43122</v>
@@ -2544,7 +2544,7 @@
         <v>1.0710209608078</v>
       </c>
       <c r="G75" t="n">
-        <v>0.954244613647461</v>
+        <v>0.954244554042816</v>
       </c>
       <c r="H75" t="n">
         <v>62338</v>
@@ -2718,7 +2718,7 @@
         <v>1.1274950504303</v>
       </c>
       <c r="G81" t="n">
-        <v>1.0045610666275</v>
+        <v>1.00456094741821</v>
       </c>
       <c r="H81" t="n">
         <v>21319</v>
@@ -2834,7 +2834,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G85" t="n">
-        <v>1.08930361270905</v>
+        <v>1.08930349349976</v>
       </c>
       <c r="H85" t="n">
         <v>16563</v>
@@ -2863,7 +2863,7 @@
         <v>1.16018998622894</v>
       </c>
       <c r="G86" t="n">
-        <v>1.03369116783142</v>
+        <v>1.03369128704071</v>
       </c>
       <c r="H86" t="n">
         <v>35930</v>
@@ -3095,7 +3095,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G94" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134019851685</v>
       </c>
       <c r="H94" t="n">
         <v>1518</v>
@@ -3153,7 +3153,7 @@
         <v>1.09975302219391</v>
       </c>
       <c r="G96" t="n">
-        <v>0.97984379529953</v>
+        <v>0.979843854904175</v>
       </c>
       <c r="H96" t="n">
         <v>2018</v>
@@ -3182,7 +3182,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G97" t="n">
-        <v>0.981609761714935</v>
+        <v>0.981609702110291</v>
       </c>
       <c r="H97" t="n">
         <v>54279</v>
@@ -3211,7 +3211,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G98" t="n">
-        <v>0.981609761714935</v>
+        <v>0.981609702110291</v>
       </c>
       <c r="H98" t="n">
         <v>7938</v>
@@ -3240,7 +3240,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G99" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134019851685</v>
       </c>
       <c r="H99" t="n">
         <v>20985</v>
@@ -3269,7 +3269,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G100" t="n">
-        <v>0.944533944129944</v>
+        <v>0.944533884525299</v>
       </c>
       <c r="H100" t="n">
         <v>12814</v>
@@ -3298,7 +3298,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971016049385071</v>
+        <v>0.971016108989716</v>
       </c>
       <c r="H101" t="n">
         <v>19652</v>
@@ -3356,7 +3356,7 @@
         <v>1.12947595119476</v>
       </c>
       <c r="G103" t="n">
-        <v>1.00632607936859</v>
+        <v>1.0063259601593</v>
       </c>
       <c r="H103" t="n">
         <v>20141</v>
@@ -3385,7 +3385,7 @@
         <v>1.11758697032928</v>
       </c>
       <c r="G104" t="n">
-        <v>0.995733261108398</v>
+        <v>0.995733320713043</v>
       </c>
       <c r="H104" t="n">
         <v>10358</v>
@@ -3443,7 +3443,7 @@
         <v>1.13443005084991</v>
       </c>
       <c r="G106" t="n">
-        <v>1.01074004173279</v>
+        <v>1.0107399225235</v>
       </c>
       <c r="H106" t="n">
         <v>17337</v>
@@ -3501,7 +3501,7 @@
         <v>1.16613495349884</v>
       </c>
       <c r="G108" t="n">
-        <v>1.03898787498474</v>
+        <v>1.03898799419403</v>
       </c>
       <c r="H108" t="n">
         <v>65162</v>
@@ -3588,7 +3588,7 @@
         <v>1.12947595119476</v>
       </c>
       <c r="G111" t="n">
-        <v>1.05007898807526</v>
+        <v>1.05007886886597</v>
       </c>
       <c r="H111" t="n">
         <v>19102</v>
@@ -3646,7 +3646,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G113" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H113" t="n">
         <v>29366</v>
@@ -3675,7 +3675,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G114" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H114" t="n">
         <v>77975</v>
@@ -3733,7 +3733,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G116" t="n">
-        <v>0.953360855579376</v>
+        <v>0.953360915184021</v>
       </c>
       <c r="H116" t="n">
         <v>15611</v>
@@ -3762,7 +3762,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G117" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H117" t="n">
         <v>9790</v>
@@ -3849,7 +3849,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G120" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H120" t="n">
         <v>8326</v>
@@ -3907,7 +3907,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G122" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H122" t="n">
         <v>4774</v>
@@ -3965,7 +3965,7 @@
         <v>0.989777982234955</v>
       </c>
       <c r="G124" t="n">
-        <v>0.920201063156128</v>
+        <v>0.920201122760773</v>
       </c>
       <c r="H124" t="n">
         <v>90762</v>
@@ -4400,7 +4400,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G139" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H139" t="n">
         <v>15649</v>
@@ -4516,7 +4516,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G143" t="n">
-        <v>0.95244038105011</v>
+        <v>0.952440440654755</v>
       </c>
       <c r="H143" t="n">
         <v>8705</v>
@@ -4545,7 +4545,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G144" t="n">
-        <v>0.944150328636169</v>
+        <v>0.944150269031525</v>
       </c>
       <c r="H144" t="n">
         <v>8451</v>
@@ -4951,7 +4951,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G158" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H158" t="n">
         <v>8684</v>
@@ -4980,7 +4980,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G159" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H159" t="n">
         <v>25293</v>
@@ -5067,7 +5067,7 @@
         <v>1.03931605815887</v>
       </c>
       <c r="G162" t="n">
-        <v>0.96625691652298</v>
+        <v>0.966256856918335</v>
       </c>
       <c r="H162" t="n">
         <v>4037</v>
@@ -5125,7 +5125,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G164" t="n">
-        <v>0.959809303283691</v>
+        <v>0.959809362888336</v>
       </c>
       <c r="H164" t="n">
         <v>4758</v>
@@ -5154,7 +5154,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G165" t="n">
-        <v>0.95244038105011</v>
+        <v>0.952440440654755</v>
       </c>
       <c r="H165" t="n">
         <v>6186</v>
@@ -5241,7 +5241,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G168" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H168" t="n">
         <v>26716</v>
@@ -5357,7 +5357,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G172" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H172" t="n">
         <v>5069</v>
@@ -5560,7 +5560,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G179" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H179" t="n">
         <v>8029</v>
@@ -5618,7 +5618,7 @@
         <v>1.09876203536987</v>
       </c>
       <c r="G181" t="n">
-        <v>1.02152407169342</v>
+        <v>1.02152395248413</v>
       </c>
       <c r="H181" t="n">
         <v>18375</v>
@@ -5879,7 +5879,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G190" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H190" t="n">
         <v>25435</v>
@@ -5937,7 +5937,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G192" t="n">
-        <v>0.986521542072296</v>
+        <v>0.986521601676941</v>
       </c>
       <c r="H192" t="n">
         <v>2493</v>
@@ -5966,7 +5966,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G193" t="n">
-        <v>0.971783936023712</v>
+        <v>0.971783995628357</v>
       </c>
       <c r="H193" t="n">
         <v>1211</v>
@@ -5995,7 +5995,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G194" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H194" t="n">
         <v>5778</v>
@@ -6169,7 +6169,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G200" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H200" t="n">
         <v>4188</v>
@@ -6227,7 +6227,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G202" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H202" t="n">
         <v>4028</v>
@@ -6256,7 +6256,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G203" t="n">
-        <v>0.964415073394775</v>
+        <v>0.96441513299942</v>
       </c>
       <c r="H203" t="n">
         <v>596</v>
@@ -6285,7 +6285,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G204" t="n">
-        <v>0.964415073394775</v>
+        <v>0.96441513299942</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>1.04129803180695</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968099534511566</v>
+        <v>0.968099474906921</v>
       </c>
       <c r="H205" t="n">
         <v>14297</v>
@@ -6343,7 +6343,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G206" t="n">
-        <v>0.971783936023712</v>
+        <v>0.971783995628357</v>
       </c>
       <c r="H206" t="n">
         <v>1110</v>
@@ -6372,7 +6372,7 @@
         <v>1.05318701267242</v>
       </c>
       <c r="G207" t="n">
-        <v>0.979152798652649</v>
+        <v>0.979152739048004</v>
       </c>
       <c r="H207" t="n">
         <v>7791</v>
@@ -6401,7 +6401,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G208" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H208" t="n">
         <v>11810</v>
@@ -6430,7 +6430,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G209" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H209" t="n">
         <v>10194</v>
@@ -6459,7 +6459,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G210" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H210" t="n">
         <v>9285</v>
@@ -6488,7 +6488,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G211" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H211" t="n">
         <v>14863</v>
@@ -6517,7 +6517,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G212" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H212" t="n">
         <v>9225</v>
@@ -6546,7 +6546,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G213" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H213" t="n">
         <v>6810</v>
@@ -6604,7 +6604,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G215" t="n">
-        <v>0.980074048042297</v>
+        <v>0.980074107646942</v>
       </c>
       <c r="H215" t="n">
         <v>13653</v>
@@ -6633,7 +6633,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G216" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H216" t="n">
         <v>8511</v>
@@ -6662,7 +6662,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G217" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H217" t="n">
         <v>1379</v>
@@ -6691,7 +6691,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G218" t="n">
-        <v>0.969019889831543</v>
+        <v>0.969019830226898</v>
       </c>
       <c r="H218" t="n">
         <v>6626</v>
@@ -6720,7 +6720,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G219" t="n">
-        <v>0.969019889831543</v>
+        <v>0.969019830226898</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.01850998401642</v>
       </c>
       <c r="G223" t="n">
-        <v>0.946913361549377</v>
+        <v>0.946913421154022</v>
       </c>
       <c r="H223" t="n">
         <v>14159</v>
@@ -6894,7 +6894,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G225" t="n">
-        <v>0.944150328636169</v>
+        <v>0.944150269031525</v>
       </c>
       <c r="H225" t="n">
         <v>2501</v>
@@ -6952,7 +6952,7 @@
         <v>1.01256501674652</v>
       </c>
       <c r="G227" t="n">
-        <v>0.941386342048645</v>
+        <v>0.941386282444</v>
       </c>
       <c r="H227" t="n">
         <v>3071</v>
@@ -6981,7 +6981,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G228" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H228" t="n">
         <v>11372</v>
@@ -7010,7 +7010,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G229" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H229" t="n">
         <v>18001</v>
@@ -7039,7 +7039,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G230" t="n">
-        <v>0.921122431755066</v>
+        <v>0.921122491359711</v>
       </c>
       <c r="H230" t="n">
         <v>8579</v>
@@ -7068,7 +7068,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G231" t="n">
-        <v>0.908226490020752</v>
+        <v>0.908226549625397</v>
       </c>
       <c r="H231" t="n">
         <v>19373</v>
@@ -7097,7 +7097,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G232" t="n">
-        <v>0.908226490020752</v>
+        <v>0.908226549625397</v>
       </c>
       <c r="H232" t="n">
         <v>3324</v>
@@ -7155,7 +7155,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G234" t="n">
-        <v>0.921122431755066</v>
+        <v>0.921122491359711</v>
       </c>
       <c r="H234" t="n">
         <v>17158</v>
@@ -7358,7 +7358,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G241" t="n">
-        <v>0.953360855579376</v>
+        <v>0.953360915184021</v>
       </c>
       <c r="H241" t="n">
         <v>15341</v>
@@ -7532,7 +7532,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G247" t="n">
-        <v>0.959809303283691</v>
+        <v>0.959809362888336</v>
       </c>
       <c r="H247" t="n">
         <v>10361</v>
@@ -7590,7 +7590,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G249" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H249" t="n">
         <v>73427</v>
@@ -7619,7 +7619,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G250" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H250" t="n">
         <v>13479</v>
@@ -7648,7 +7648,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G251" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H251" t="n">
         <v>36869</v>
@@ -7677,7 +7677,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G252" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H252" t="n">
         <v>4734</v>
@@ -7706,7 +7706,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G253" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H253" t="n">
         <v>12686</v>
@@ -7793,7 +7793,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G256" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H256" t="n">
         <v>2465</v>
@@ -7909,7 +7909,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G260" t="n">
-        <v>0.986521542072296</v>
+        <v>0.986521601676941</v>
       </c>
       <c r="H260" t="n">
         <v>12963</v>
@@ -8025,7 +8025,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G264" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H264" t="n">
         <v>18431</v>
@@ -8199,7 +8199,7 @@
         <v>1.09182703495026</v>
       </c>
       <c r="G270" t="n">
-        <v>1.01507663726807</v>
+        <v>1.01507651805878</v>
       </c>
       <c r="H270" t="n">
         <v>5995</v>
@@ -8286,7 +8286,7 @@
         <v>1.1086699962616</v>
       </c>
       <c r="G273" t="n">
-        <v>1.03073561191559</v>
+        <v>1.0307354927063</v>
       </c>
       <c r="H273" t="n">
         <v>17630</v>
@@ -8373,7 +8373,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G276" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H276" t="n">
         <v>9941</v>
@@ -8460,7 +8460,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G279" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H279" t="n">
         <v>504</v>
@@ -8547,7 +8547,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G282" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H282" t="n">
         <v>2869</v>
@@ -8576,7 +8576,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G283" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H283" t="n">
         <v>201</v>
@@ -8605,7 +8605,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G284" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H284" t="n">
         <v>19922</v>
@@ -8634,7 +8634,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G285" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H285" t="n">
         <v>6055</v>
@@ -8663,7 +8663,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G286" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H286" t="n">
         <v>4022</v>
@@ -8692,7 +8692,7 @@
         <v>1.06210398674011</v>
       </c>
       <c r="G287" t="n">
-        <v>0.987442910671234</v>
+        <v>0.987442851066589</v>
       </c>
       <c r="H287" t="n">
         <v>5271</v>
@@ -8721,7 +8721,7 @@
         <v>1.0650759935379</v>
       </c>
       <c r="G288" t="n">
-        <v>0.990205943584442</v>
+        <v>0.990206062793732</v>
       </c>
       <c r="H288" t="n">
         <v>23250</v>
@@ -8750,7 +8750,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G289" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H289" t="n">
         <v>11556</v>
@@ -8779,7 +8779,7 @@
         <v>1.05615901947021</v>
       </c>
       <c r="G290" t="n">
-        <v>0.981915891170502</v>
+        <v>0.981915831565857</v>
       </c>
       <c r="H290" t="n">
         <v>2424</v>
@@ -8808,7 +8808,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G291" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H291" t="n">
         <v>5183</v>
@@ -8837,7 +8837,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G292" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H292" t="n">
         <v>2704</v>
@@ -8866,7 +8866,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G293" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H293" t="n">
         <v>630</v>
@@ -8953,7 +8953,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G296" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H296" t="n">
         <v>413</v>
@@ -9011,7 +9011,7 @@
         <v>1.11263298988342</v>
       </c>
       <c r="G298" t="n">
-        <v>1.03442001342773</v>
+        <v>1.03441989421844</v>
       </c>
       <c r="H298" t="n">
         <v>10092</v>
@@ -9185,7 +9185,7 @@
         <v>1.21270096302032</v>
       </c>
       <c r="G304" t="n">
-        <v>1.12745356559753</v>
+        <v>1.12745368480682</v>
       </c>
       <c r="H304" t="n">
         <v>345383</v>
@@ -9272,7 +9272,7 @@
         <v>1.16613495349884</v>
       </c>
       <c r="G307" t="n">
-        <v>1.08416092395782</v>
+        <v>1.08416104316711</v>
       </c>
       <c r="H307" t="n">
         <v>147608</v>
@@ -9330,7 +9330,7 @@
         <v>1.17802405357361</v>
       </c>
       <c r="G309" t="n">
-        <v>1.09521436691284</v>
+        <v>1.09521424770355</v>
       </c>
       <c r="H309" t="n">
         <v>32265</v>
@@ -9359,7 +9359,7 @@
         <v>1.1869410276413</v>
       </c>
       <c r="G310" t="n">
-        <v>1.10350453853607</v>
+        <v>1.10350441932678</v>
       </c>
       <c r="H310" t="n">
         <v>4885</v>
@@ -9504,7 +9504,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G315" t="n">
-        <v>1.13666427135468</v>
+        <v>1.13666415214539</v>
       </c>
       <c r="H315" t="n">
         <v>59543</v>
@@ -9533,7 +9533,7 @@
         <v>1.21864497661591</v>
       </c>
       <c r="G316" t="n">
-        <v>1.13297986984253</v>
+        <v>1.13297975063324</v>
       </c>
       <c r="H316" t="n">
         <v>100407</v>
@@ -9591,7 +9591,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G318" t="n">
-        <v>1.13666427135468</v>
+        <v>1.13666415214539</v>
       </c>
       <c r="H318" t="n">
         <v>22044</v>
@@ -9736,7 +9736,7 @@
         <v>1.31673204898834</v>
       </c>
       <c r="G323" t="n">
-        <v>1.22417187690735</v>
+        <v>1.22417175769806</v>
       </c>
       <c r="H323" t="n">
         <v>194343</v>
@@ -9852,7 +9852,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G327" t="n">
-        <v>1.1799578666687</v>
+        <v>1.17995774745941</v>
       </c>
       <c r="H327" t="n">
         <v>102280</v>
@@ -9939,7 +9939,7 @@
         <v>1.29889798164368</v>
       </c>
       <c r="G330" t="n">
-        <v>1.2075914144516</v>
+        <v>1.20759129524231</v>
       </c>
       <c r="H330" t="n">
         <v>47401</v>
@@ -9968,7 +9968,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G331" t="n">
-        <v>1.16521918773651</v>
+        <v>1.16521906852722</v>
       </c>
       <c r="H331" t="n">
         <v>142707</v>
@@ -10200,7 +10200,7 @@
         <v>1.22954404354095</v>
       </c>
       <c r="G339" t="n">
-        <v>1.14311265945435</v>
+        <v>1.14311277866364</v>
       </c>
       <c r="H339" t="n">
         <v>15944</v>
@@ -10287,7 +10287,7 @@
         <v>1.19783902168274</v>
       </c>
       <c r="G342" t="n">
-        <v>1.11363649368286</v>
+        <v>1.11363637447357</v>
       </c>
       <c r="H342" t="n">
         <v>10206</v>
@@ -10316,7 +10316,7 @@
         <v>1.19585800170898</v>
       </c>
       <c r="G343" t="n">
-        <v>1.11179459095001</v>
+        <v>1.1117947101593</v>
       </c>
       <c r="H343" t="n">
         <v>48580</v>
@@ -10345,7 +10345,7 @@
         <v>1.20378398895264</v>
       </c>
       <c r="G344" t="n">
-        <v>1.11916351318359</v>
+        <v>1.1191633939743</v>
       </c>
       <c r="H344" t="n">
         <v>24146</v>
@@ -10374,7 +10374,7 @@
         <v>1.22657203674316</v>
       </c>
       <c r="G345" t="n">
-        <v>1.14034962654114</v>
+        <v>1.14034950733185</v>
       </c>
       <c r="H345" t="n">
         <v>16104</v>
@@ -10461,7 +10461,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G348" t="n">
-        <v>1.16521918773651</v>
+        <v>1.16521906852722</v>
       </c>
       <c r="H348" t="n">
         <v>32469</v>
@@ -10519,7 +10519,7 @@
         <v>1.31375896930695</v>
       </c>
       <c r="G350" t="n">
-        <v>1.22140777111053</v>
+        <v>1.22140765190125</v>
       </c>
       <c r="H350" t="n">
         <v>171747</v>
@@ -10606,7 +10606,7 @@
         <v>1.26719295978546</v>
       </c>
       <c r="G353" t="n">
-        <v>1.17811512947083</v>
+        <v>1.17811501026154</v>
       </c>
       <c r="H353" t="n">
         <v>40097</v>
@@ -10635,7 +10635,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G354" t="n">
-        <v>1.1799578666687</v>
+        <v>1.17995774745941</v>
       </c>
       <c r="H354" t="n">
         <v>25472</v>
@@ -10809,7 +10809,7 @@
         <v>1.35834395885468</v>
       </c>
       <c r="G360" t="n">
-        <v>1.26285862922668</v>
+        <v>1.2628585100174</v>
       </c>
       <c r="H360" t="n">
         <v>4290</v>
@@ -79980,6 +79980,35 @@
         <v>3396</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.263000011444092</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.275999993085861</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.263000011444092</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.273999989032745</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.273999989032745</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>15044</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.939238011837006</v>
+        <v>0.939237952232361</v>
       </c>
       <c r="H3" t="n">
         <v>17307</v>
@@ -485,7 +485,7 @@
         <v>1.04030704498291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926879465579987</v>
+        <v>0.926879405975342</v>
       </c>
       <c r="H4" t="n">
         <v>6401</v>
@@ -514,7 +514,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.910106956958771</v>
+        <v>0.910106897354126</v>
       </c>
       <c r="H5" t="n">
         <v>44193</v>
@@ -601,7 +601,7 @@
         <v>1.01058399677277</v>
       </c>
       <c r="G8" t="n">
-        <v>0.900397181510925</v>
+        <v>0.900397121906281</v>
       </c>
       <c r="H8" t="n">
         <v>23254</v>
@@ -630,7 +630,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910106956958771</v>
+        <v>0.910106897354126</v>
       </c>
       <c r="H9" t="n">
         <v>24329</v>
@@ -659,7 +659,7 @@
         <v>1.02049195766449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.909224808216095</v>
+        <v>0.90922486782074</v>
       </c>
       <c r="H10" t="n">
         <v>2966</v>
@@ -688,7 +688,7 @@
         <v>0.998695015907288</v>
       </c>
       <c r="G11" t="n">
-        <v>0.889804422855377</v>
+        <v>0.889804482460022</v>
       </c>
       <c r="H11" t="n">
         <v>63536</v>
@@ -804,7 +804,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G15" t="n">
-        <v>0.882742702960968</v>
+        <v>0.882742643356323</v>
       </c>
       <c r="H15" t="n">
         <v>17895</v>
@@ -891,7 +891,7 @@
         <v>0.951138019561768</v>
       </c>
       <c r="G18" t="n">
-        <v>0.847432792186737</v>
+        <v>0.847432732582092</v>
       </c>
       <c r="H18" t="n">
         <v>8438</v>
@@ -920,7 +920,7 @@
         <v>0.970457971096039</v>
       </c>
       <c r="G19" t="n">
-        <v>0.864646255970001</v>
+        <v>0.864646196365356</v>
       </c>
       <c r="H19" t="n">
         <v>3784</v>
@@ -949,7 +949,7 @@
         <v>0.968972027301788</v>
       </c>
       <c r="G20" t="n">
-        <v>0.863322257995605</v>
+        <v>0.86332231760025</v>
       </c>
       <c r="H20" t="n">
         <v>1418</v>
@@ -1268,7 +1268,7 @@
         <v>0.790633022785187</v>
       </c>
       <c r="G31" t="n">
-        <v>0.70442807674408</v>
+        <v>0.704428136348724</v>
       </c>
       <c r="H31" t="n">
         <v>7569</v>
@@ -1558,7 +1558,7 @@
         <v>0.910516023635864</v>
       </c>
       <c r="G41" t="n">
-        <v>0.811239898204803</v>
+        <v>0.811239838600159</v>
       </c>
       <c r="H41" t="n">
         <v>26265</v>
@@ -1616,7 +1616,7 @@
         <v>0.965503990650177</v>
       </c>
       <c r="G43" t="n">
-        <v>0.860232412815094</v>
+        <v>0.860232353210449</v>
       </c>
       <c r="H43" t="n">
         <v>5234</v>
@@ -1732,7 +1732,7 @@
         <v>0.946183979511261</v>
       </c>
       <c r="G47" t="n">
-        <v>0.84301882982254</v>
+        <v>0.843018889427185</v>
       </c>
       <c r="H47" t="n">
         <v>9568</v>
@@ -1819,7 +1819,7 @@
         <v>0.924881994724274</v>
       </c>
       <c r="G50" t="n">
-        <v>0.82403951883316</v>
+        <v>0.824039459228516</v>
       </c>
       <c r="H50" t="n">
         <v>7700</v>
@@ -1848,7 +1848,7 @@
         <v>0.920423984527588</v>
       </c>
       <c r="G51" t="n">
-        <v>0.820067524909973</v>
+        <v>0.820067584514618</v>
       </c>
       <c r="H51" t="n">
         <v>5213</v>
@@ -2109,7 +2109,7 @@
         <v>0.935781002044678</v>
       </c>
       <c r="G60" t="n">
-        <v>0.833750128746033</v>
+        <v>0.833750188350677</v>
       </c>
       <c r="H60" t="n">
         <v>4464</v>
@@ -2196,7 +2196,7 @@
         <v>0.95856899023056</v>
       </c>
       <c r="G63" t="n">
-        <v>0.854053497314453</v>
+        <v>0.854053556919098</v>
       </c>
       <c r="H63" t="n">
         <v>17257</v>
@@ -2283,7 +2283,7 @@
         <v>0.952624022960663</v>
       </c>
       <c r="G66" t="n">
-        <v>0.848756730556488</v>
+        <v>0.848756670951843</v>
       </c>
       <c r="H66" t="n">
         <v>10698</v>
@@ -2312,7 +2312,7 @@
         <v>0.971943974494934</v>
       </c>
       <c r="G67" t="n">
-        <v>0.865970194339752</v>
+        <v>0.865970134735107</v>
       </c>
       <c r="H67" t="n">
         <v>10093</v>
@@ -2399,7 +2399,7 @@
         <v>0.957081973552704</v>
       </c>
       <c r="G70" t="n">
-        <v>0.852728664875031</v>
+        <v>0.852728605270386</v>
       </c>
       <c r="H70" t="n">
         <v>20319</v>
@@ -2428,7 +2428,7 @@
         <v>0.979870021343231</v>
       </c>
       <c r="G71" t="n">
-        <v>0.873031973838806</v>
+        <v>0.873032033443451</v>
       </c>
       <c r="H71" t="n">
         <v>1148</v>
@@ -2486,7 +2486,7 @@
         <v>1.01652801036835</v>
       </c>
       <c r="G73" t="n">
-        <v>0.905693113803864</v>
+        <v>0.905693054199219</v>
       </c>
       <c r="H73" t="n">
         <v>22149</v>
@@ -2515,7 +2515,7 @@
         <v>1.05814099311829</v>
       </c>
       <c r="G74" t="n">
-        <v>0.942768931388855</v>
+        <v>0.94276887178421</v>
       </c>
       <c r="H74" t="n">
         <v>43122</v>
@@ -2573,7 +2573,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G76" t="n">
-        <v>0.986905694007874</v>
+        <v>0.986905634403229</v>
       </c>
       <c r="H76" t="n">
         <v>69226</v>
@@ -2602,7 +2602,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G77" t="n">
-        <v>0.997498333454132</v>
+        <v>0.997498393058777</v>
       </c>
       <c r="H77" t="n">
         <v>75982</v>
@@ -2631,7 +2631,7 @@
         <v>1.18595004081726</v>
       </c>
       <c r="G78" t="n">
-        <v>1.05664253234863</v>
+        <v>1.05664265155792</v>
       </c>
       <c r="H78" t="n">
         <v>93047</v>
@@ -2718,7 +2718,7 @@
         <v>1.1274950504303</v>
       </c>
       <c r="G81" t="n">
-        <v>1.00456094741821</v>
+        <v>1.0045610666275</v>
       </c>
       <c r="H81" t="n">
         <v>21319</v>
@@ -2805,7 +2805,7 @@
         <v>1.19982099533081</v>
       </c>
       <c r="G84" t="n">
-        <v>1.06900119781494</v>
+        <v>1.06900107860565</v>
       </c>
       <c r="H84" t="n">
         <v>17658</v>
@@ -2834,7 +2834,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G85" t="n">
-        <v>1.08930349349976</v>
+        <v>1.08930361270905</v>
       </c>
       <c r="H85" t="n">
         <v>16563</v>
@@ -2863,7 +2863,7 @@
         <v>1.16018998622894</v>
       </c>
       <c r="G86" t="n">
-        <v>1.03369128704071</v>
+        <v>1.03369116783142</v>
       </c>
       <c r="H86" t="n">
         <v>35930</v>
@@ -2950,7 +2950,7 @@
         <v>1.13641202449799</v>
       </c>
       <c r="G89" t="n">
-        <v>1.0125058889389</v>
+        <v>1.01250576972961</v>
       </c>
       <c r="H89" t="n">
         <v>15210</v>
@@ -3037,7 +3037,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G92" t="n">
-        <v>0.986905694007874</v>
+        <v>0.986905634403229</v>
       </c>
       <c r="H92" t="n">
         <v>21899</v>
@@ -3066,7 +3066,7 @@
         <v>1.10569798946381</v>
       </c>
       <c r="G93" t="n">
-        <v>0.98514062166214</v>
+        <v>0.985140681266785</v>
       </c>
       <c r="H93" t="n">
         <v>45101</v>
@@ -3095,7 +3095,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G94" t="n">
-        <v>0.970134019851685</v>
+        <v>0.970134079456329</v>
       </c>
       <c r="H94" t="n">
         <v>1518</v>
@@ -3124,7 +3124,7 @@
         <v>1.07795596122742</v>
       </c>
       <c r="G95" t="n">
-        <v>0.960423409938812</v>
+        <v>0.960423350334167</v>
       </c>
       <c r="H95" t="n">
         <v>45454</v>
@@ -3240,7 +3240,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G99" t="n">
-        <v>0.970134019851685</v>
+        <v>0.970134079456329</v>
       </c>
       <c r="H99" t="n">
         <v>20985</v>
@@ -3269,7 +3269,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G100" t="n">
-        <v>0.944533884525299</v>
+        <v>0.944533944129944</v>
       </c>
       <c r="H100" t="n">
         <v>12814</v>
@@ -3298,7 +3298,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971016108989716</v>
+        <v>0.971015989780426</v>
       </c>
       <c r="H101" t="n">
         <v>19652</v>
@@ -3327,7 +3327,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G102" t="n">
-        <v>0.997498333454132</v>
+        <v>0.997498393058777</v>
       </c>
       <c r="H102" t="n">
         <v>21901</v>
@@ -3385,7 +3385,7 @@
         <v>1.11758697032928</v>
       </c>
       <c r="G104" t="n">
-        <v>0.995733320713043</v>
+        <v>0.995733201503754</v>
       </c>
       <c r="H104" t="n">
         <v>10358</v>
@@ -3588,7 +3588,7 @@
         <v>1.12947595119476</v>
       </c>
       <c r="G111" t="n">
-        <v>1.05007886886597</v>
+        <v>1.05007898807526</v>
       </c>
       <c r="H111" t="n">
         <v>19102</v>
@@ -3646,7 +3646,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G113" t="n">
-        <v>0.99296909570694</v>
+        <v>0.992969155311584</v>
       </c>
       <c r="H113" t="n">
         <v>29366</v>
@@ -3675,7 +3675,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G114" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H114" t="n">
         <v>77975</v>
@@ -3733,7 +3733,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G116" t="n">
-        <v>0.953360915184021</v>
+        <v>0.953360855579376</v>
       </c>
       <c r="H116" t="n">
         <v>15611</v>
@@ -3762,7 +3762,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G117" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H117" t="n">
         <v>9790</v>
@@ -3849,7 +3849,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G120" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H120" t="n">
         <v>8326</v>
@@ -3907,7 +3907,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G122" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H122" t="n">
         <v>4774</v>
@@ -3965,7 +3965,7 @@
         <v>0.989777982234955</v>
       </c>
       <c r="G124" t="n">
-        <v>0.920201122760773</v>
+        <v>0.920201063156128</v>
       </c>
       <c r="H124" t="n">
         <v>90762</v>
@@ -4400,7 +4400,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G139" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H139" t="n">
         <v>15649</v>
@@ -4516,7 +4516,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G143" t="n">
-        <v>0.952440440654755</v>
+        <v>0.95244038105011</v>
       </c>
       <c r="H143" t="n">
         <v>8705</v>
@@ -4545,7 +4545,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G144" t="n">
-        <v>0.944150269031525</v>
+        <v>0.944150328636169</v>
       </c>
       <c r="H144" t="n">
         <v>8451</v>
@@ -4951,7 +4951,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G158" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H158" t="n">
         <v>8684</v>
@@ -4980,7 +4980,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G159" t="n">
-        <v>0.993890345096588</v>
+        <v>0.993890404701233</v>
       </c>
       <c r="H159" t="n">
         <v>25293</v>
@@ -5067,7 +5067,7 @@
         <v>1.03931605815887</v>
       </c>
       <c r="G162" t="n">
-        <v>0.966256856918335</v>
+        <v>0.96625691652298</v>
       </c>
       <c r="H162" t="n">
         <v>4037</v>
@@ -5125,7 +5125,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G164" t="n">
-        <v>0.959809362888336</v>
+        <v>0.959809303283691</v>
       </c>
       <c r="H164" t="n">
         <v>4758</v>
@@ -5154,7 +5154,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G165" t="n">
-        <v>0.952440440654755</v>
+        <v>0.95244038105011</v>
       </c>
       <c r="H165" t="n">
         <v>6186</v>
@@ -5241,7 +5241,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G168" t="n">
-        <v>0.993890345096588</v>
+        <v>0.993890404701233</v>
       </c>
       <c r="H168" t="n">
         <v>26716</v>
@@ -5357,7 +5357,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G172" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H172" t="n">
         <v>5069</v>
@@ -5560,7 +5560,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G179" t="n">
-        <v>0.996654331684113</v>
+        <v>0.996654391288757</v>
       </c>
       <c r="H179" t="n">
         <v>8029</v>
@@ -5618,7 +5618,7 @@
         <v>1.09876203536987</v>
       </c>
       <c r="G181" t="n">
-        <v>1.02152395248413</v>
+        <v>1.02152407169342</v>
       </c>
       <c r="H181" t="n">
         <v>18375</v>
@@ -5879,7 +5879,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G190" t="n">
-        <v>0.994811713695526</v>
+        <v>0.994811773300171</v>
       </c>
       <c r="H190" t="n">
         <v>25435</v>
@@ -5937,7 +5937,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G192" t="n">
-        <v>0.986521601676941</v>
+        <v>0.986521542072296</v>
       </c>
       <c r="H192" t="n">
         <v>2493</v>
@@ -5966,7 +5966,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G193" t="n">
-        <v>0.971783995628357</v>
+        <v>0.971783936023712</v>
       </c>
       <c r="H193" t="n">
         <v>1211</v>
@@ -5995,7 +5995,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G194" t="n">
-        <v>0.993890345096588</v>
+        <v>0.993890404701233</v>
       </c>
       <c r="H194" t="n">
         <v>5778</v>
@@ -6169,7 +6169,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G200" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H200" t="n">
         <v>4188</v>
@@ -6227,7 +6227,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G202" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H202" t="n">
         <v>4028</v>
@@ -6256,7 +6256,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G203" t="n">
-        <v>0.96441513299942</v>
+        <v>0.964415073394775</v>
       </c>
       <c r="H203" t="n">
         <v>596</v>
@@ -6285,7 +6285,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G204" t="n">
-        <v>0.96441513299942</v>
+        <v>0.964415073394775</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>1.04129803180695</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968099474906921</v>
+        <v>0.968099534511566</v>
       </c>
       <c r="H205" t="n">
         <v>14297</v>
@@ -6343,7 +6343,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G206" t="n">
-        <v>0.971783995628357</v>
+        <v>0.971783936023712</v>
       </c>
       <c r="H206" t="n">
         <v>1110</v>
@@ -6372,7 +6372,7 @@
         <v>1.05318701267242</v>
       </c>
       <c r="G207" t="n">
-        <v>0.979152739048004</v>
+        <v>0.979152798652649</v>
       </c>
       <c r="H207" t="n">
         <v>7791</v>
@@ -6401,7 +6401,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G208" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H208" t="n">
         <v>11810</v>
@@ -6430,7 +6430,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G209" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H209" t="n">
         <v>10194</v>
@@ -6459,7 +6459,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G210" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H210" t="n">
         <v>9285</v>
@@ -6488,7 +6488,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G211" t="n">
-        <v>0.99296909570694</v>
+        <v>0.992969155311584</v>
       </c>
       <c r="H211" t="n">
         <v>14863</v>
@@ -6517,7 +6517,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G212" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H212" t="n">
         <v>9225</v>
@@ -6546,7 +6546,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G213" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H213" t="n">
         <v>6810</v>
@@ -6604,7 +6604,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G215" t="n">
-        <v>0.980074107646942</v>
+        <v>0.980074048042297</v>
       </c>
       <c r="H215" t="n">
         <v>13653</v>
@@ -6633,7 +6633,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G216" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H216" t="n">
         <v>8511</v>
@@ -6662,7 +6662,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G217" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H217" t="n">
         <v>1379</v>
@@ -6691,7 +6691,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G218" t="n">
-        <v>0.969019830226898</v>
+        <v>0.969019889831543</v>
       </c>
       <c r="H218" t="n">
         <v>6626</v>
@@ -6720,7 +6720,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G219" t="n">
-        <v>0.969019830226898</v>
+        <v>0.969019889831543</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.01850998401642</v>
       </c>
       <c r="G223" t="n">
-        <v>0.946913421154022</v>
+        <v>0.946913361549377</v>
       </c>
       <c r="H223" t="n">
         <v>14159</v>
@@ -6894,7 +6894,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G225" t="n">
-        <v>0.944150269031525</v>
+        <v>0.944150328636169</v>
       </c>
       <c r="H225" t="n">
         <v>2501</v>
@@ -6952,7 +6952,7 @@
         <v>1.01256501674652</v>
       </c>
       <c r="G227" t="n">
-        <v>0.941386282444</v>
+        <v>0.941386342048645</v>
       </c>
       <c r="H227" t="n">
         <v>3071</v>
@@ -6981,7 +6981,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G228" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H228" t="n">
         <v>11372</v>
@@ -7010,7 +7010,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G229" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H229" t="n">
         <v>18001</v>
@@ -7039,7 +7039,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G230" t="n">
-        <v>0.921122491359711</v>
+        <v>0.921122431755066</v>
       </c>
       <c r="H230" t="n">
         <v>8579</v>
@@ -7068,7 +7068,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G231" t="n">
-        <v>0.908226549625397</v>
+        <v>0.908226490020752</v>
       </c>
       <c r="H231" t="n">
         <v>19373</v>
@@ -7097,7 +7097,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G232" t="n">
-        <v>0.908226549625397</v>
+        <v>0.908226490020752</v>
       </c>
       <c r="H232" t="n">
         <v>3324</v>
@@ -7155,7 +7155,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G234" t="n">
-        <v>0.921122491359711</v>
+        <v>0.921122431755066</v>
       </c>
       <c r="H234" t="n">
         <v>17158</v>
@@ -7358,7 +7358,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G241" t="n">
-        <v>0.953360915184021</v>
+        <v>0.953360855579376</v>
       </c>
       <c r="H241" t="n">
         <v>15341</v>
@@ -7532,7 +7532,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G247" t="n">
-        <v>0.959809362888336</v>
+        <v>0.959809303283691</v>
       </c>
       <c r="H247" t="n">
         <v>10361</v>
@@ -7590,7 +7590,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G249" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H249" t="n">
         <v>73427</v>
@@ -7619,7 +7619,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G250" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H250" t="n">
         <v>13479</v>
@@ -7648,7 +7648,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G251" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H251" t="n">
         <v>36869</v>
@@ -7677,7 +7677,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G252" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H252" t="n">
         <v>4734</v>
@@ -7706,7 +7706,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G253" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H253" t="n">
         <v>12686</v>
@@ -7793,7 +7793,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G256" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H256" t="n">
         <v>2465</v>
@@ -7909,7 +7909,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G260" t="n">
-        <v>0.986521601676941</v>
+        <v>0.986521542072296</v>
       </c>
       <c r="H260" t="n">
         <v>12963</v>
@@ -8025,7 +8025,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G264" t="n">
-        <v>0.994811713695526</v>
+        <v>0.994811773300171</v>
       </c>
       <c r="H264" t="n">
         <v>18431</v>
@@ -8199,7 +8199,7 @@
         <v>1.09182703495026</v>
       </c>
       <c r="G270" t="n">
-        <v>1.01507651805878</v>
+        <v>1.01507663726807</v>
       </c>
       <c r="H270" t="n">
         <v>5995</v>
@@ -8286,7 +8286,7 @@
         <v>1.1086699962616</v>
       </c>
       <c r="G273" t="n">
-        <v>1.0307354927063</v>
+        <v>1.03073561191559</v>
       </c>
       <c r="H273" t="n">
         <v>17630</v>
@@ -8373,7 +8373,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G276" t="n">
-        <v>0.996654331684113</v>
+        <v>0.996654391288757</v>
       </c>
       <c r="H276" t="n">
         <v>9941</v>
@@ -8460,7 +8460,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G279" t="n">
-        <v>0.996654331684113</v>
+        <v>0.996654391288757</v>
       </c>
       <c r="H279" t="n">
         <v>504</v>
@@ -8547,7 +8547,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G282" t="n">
-        <v>0.994811713695526</v>
+        <v>0.994811773300171</v>
       </c>
       <c r="H282" t="n">
         <v>2869</v>
@@ -8576,7 +8576,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G283" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H283" t="n">
         <v>201</v>
@@ -8605,7 +8605,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G284" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H284" t="n">
         <v>19922</v>
@@ -8634,7 +8634,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G285" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H285" t="n">
         <v>6055</v>
@@ -8663,7 +8663,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G286" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H286" t="n">
         <v>4022</v>
@@ -8692,7 +8692,7 @@
         <v>1.06210398674011</v>
       </c>
       <c r="G287" t="n">
-        <v>0.987442851066589</v>
+        <v>0.987442910671234</v>
       </c>
       <c r="H287" t="n">
         <v>5271</v>
@@ -8721,7 +8721,7 @@
         <v>1.0650759935379</v>
       </c>
       <c r="G288" t="n">
-        <v>0.990206062793732</v>
+        <v>0.990205943584442</v>
       </c>
       <c r="H288" t="n">
         <v>23250</v>
@@ -8750,7 +8750,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G289" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H289" t="n">
         <v>11556</v>
@@ -8779,7 +8779,7 @@
         <v>1.05615901947021</v>
       </c>
       <c r="G290" t="n">
-        <v>0.981915831565857</v>
+        <v>0.981915891170502</v>
       </c>
       <c r="H290" t="n">
         <v>2424</v>
@@ -8808,7 +8808,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G291" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H291" t="n">
         <v>5183</v>
@@ -8837,7 +8837,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G292" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H292" t="n">
         <v>2704</v>
@@ -8866,7 +8866,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G293" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H293" t="n">
         <v>630</v>
@@ -8953,7 +8953,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G296" t="n">
-        <v>0.99296909570694</v>
+        <v>0.992969155311584</v>
       </c>
       <c r="H296" t="n">
         <v>413</v>
@@ -9011,7 +9011,7 @@
         <v>1.11263298988342</v>
       </c>
       <c r="G298" t="n">
-        <v>1.03441989421844</v>
+        <v>1.03442001342773</v>
       </c>
       <c r="H298" t="n">
         <v>10092</v>
@@ -9185,7 +9185,7 @@
         <v>1.21270096302032</v>
       </c>
       <c r="G304" t="n">
-        <v>1.12745368480682</v>
+        <v>1.12745356559753</v>
       </c>
       <c r="H304" t="n">
         <v>345383</v>
@@ -9272,7 +9272,7 @@
         <v>1.16613495349884</v>
       </c>
       <c r="G307" t="n">
-        <v>1.08416104316711</v>
+        <v>1.08416092395782</v>
       </c>
       <c r="H307" t="n">
         <v>147608</v>
@@ -9330,7 +9330,7 @@
         <v>1.17802405357361</v>
       </c>
       <c r="G309" t="n">
-        <v>1.09521424770355</v>
+        <v>1.09521436691284</v>
       </c>
       <c r="H309" t="n">
         <v>32265</v>
@@ -9359,7 +9359,7 @@
         <v>1.1869410276413</v>
       </c>
       <c r="G310" t="n">
-        <v>1.10350441932678</v>
+        <v>1.10350453853607</v>
       </c>
       <c r="H310" t="n">
         <v>4885</v>
@@ -9504,7 +9504,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G315" t="n">
-        <v>1.13666415214539</v>
+        <v>1.13666427135468</v>
       </c>
       <c r="H315" t="n">
         <v>59543</v>
@@ -9533,7 +9533,7 @@
         <v>1.21864497661591</v>
       </c>
       <c r="G316" t="n">
-        <v>1.13297975063324</v>
+        <v>1.13297986984253</v>
       </c>
       <c r="H316" t="n">
         <v>100407</v>
@@ -9591,7 +9591,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G318" t="n">
-        <v>1.13666415214539</v>
+        <v>1.13666427135468</v>
       </c>
       <c r="H318" t="n">
         <v>22044</v>
@@ -9736,7 +9736,7 @@
         <v>1.31673204898834</v>
       </c>
       <c r="G323" t="n">
-        <v>1.22417175769806</v>
+        <v>1.22417187690735</v>
       </c>
       <c r="H323" t="n">
         <v>194343</v>
@@ -9852,7 +9852,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G327" t="n">
-        <v>1.17995774745941</v>
+        <v>1.1799578666687</v>
       </c>
       <c r="H327" t="n">
         <v>102280</v>
@@ -9939,7 +9939,7 @@
         <v>1.29889798164368</v>
       </c>
       <c r="G330" t="n">
-        <v>1.20759129524231</v>
+        <v>1.2075914144516</v>
       </c>
       <c r="H330" t="n">
         <v>47401</v>
@@ -9968,7 +9968,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G331" t="n">
-        <v>1.16521906852722</v>
+        <v>1.16521918773651</v>
       </c>
       <c r="H331" t="n">
         <v>142707</v>
@@ -10200,7 +10200,7 @@
         <v>1.22954404354095</v>
       </c>
       <c r="G339" t="n">
-        <v>1.14311277866364</v>
+        <v>1.14311265945435</v>
       </c>
       <c r="H339" t="n">
         <v>15944</v>
@@ -10287,7 +10287,7 @@
         <v>1.19783902168274</v>
       </c>
       <c r="G342" t="n">
-        <v>1.11363637447357</v>
+        <v>1.11363649368286</v>
       </c>
       <c r="H342" t="n">
         <v>10206</v>
@@ -10316,7 +10316,7 @@
         <v>1.19585800170898</v>
       </c>
       <c r="G343" t="n">
-        <v>1.1117947101593</v>
+        <v>1.11179459095001</v>
       </c>
       <c r="H343" t="n">
         <v>48580</v>
@@ -10345,7 +10345,7 @@
         <v>1.20378398895264</v>
       </c>
       <c r="G344" t="n">
-        <v>1.1191633939743</v>
+        <v>1.11916351318359</v>
       </c>
       <c r="H344" t="n">
         <v>24146</v>
@@ -10374,7 +10374,7 @@
         <v>1.22657203674316</v>
       </c>
       <c r="G345" t="n">
-        <v>1.14034950733185</v>
+        <v>1.14034962654114</v>
       </c>
       <c r="H345" t="n">
         <v>16104</v>
@@ -10461,7 +10461,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G348" t="n">
-        <v>1.16521906852722</v>
+        <v>1.16521918773651</v>
       </c>
       <c r="H348" t="n">
         <v>32469</v>
@@ -10519,7 +10519,7 @@
         <v>1.31375896930695</v>
       </c>
       <c r="G350" t="n">
-        <v>1.22140765190125</v>
+        <v>1.22140777111053</v>
       </c>
       <c r="H350" t="n">
         <v>171747</v>
@@ -10606,7 +10606,7 @@
         <v>1.26719295978546</v>
       </c>
       <c r="G353" t="n">
-        <v>1.17811501026154</v>
+        <v>1.17811512947083</v>
       </c>
       <c r="H353" t="n">
         <v>40097</v>
@@ -10635,7 +10635,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G354" t="n">
-        <v>1.17995774745941</v>
+        <v>1.1799578666687</v>
       </c>
       <c r="H354" t="n">
         <v>25472</v>
@@ -10809,7 +10809,7 @@
         <v>1.35834395885468</v>
       </c>
       <c r="G360" t="n">
-        <v>1.2628585100174</v>
+        <v>1.26285862922668</v>
       </c>
       <c r="H360" t="n">
         <v>4290</v>
@@ -80009,6 +80009,35 @@
         <v>15044</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.266000002622604</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.266000002622604</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>9621</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.939237952232361</v>
+        <v>0.939238011837006</v>
       </c>
       <c r="H3" t="n">
         <v>17307</v>
@@ -485,7 +485,7 @@
         <v>1.04030704498291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926879405975342</v>
+        <v>0.926879465579987</v>
       </c>
       <c r="H4" t="n">
         <v>6401</v>
@@ -514,7 +514,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H5" t="n">
         <v>44193</v>
@@ -630,7 +630,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H9" t="n">
         <v>24329</v>
@@ -659,7 +659,7 @@
         <v>1.02049195766449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.90922486782074</v>
+        <v>0.909224808216095</v>
       </c>
       <c r="H10" t="n">
         <v>2966</v>
@@ -891,7 +891,7 @@
         <v>0.951138019561768</v>
       </c>
       <c r="G18" t="n">
-        <v>0.847432732582092</v>
+        <v>0.847432792186737</v>
       </c>
       <c r="H18" t="n">
         <v>8438</v>
@@ -1007,7 +1007,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G22" t="n">
-        <v>0.85625958442688</v>
+        <v>0.856259524822235</v>
       </c>
       <c r="H22" t="n">
         <v>10047</v>
@@ -1065,7 +1065,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G24" t="n">
-        <v>0.812122821807861</v>
+        <v>0.812122881412506</v>
       </c>
       <c r="H24" t="n">
         <v>12656</v>
@@ -1181,7 +1181,7 @@
         <v>0.824814975261688</v>
       </c>
       <c r="G28" t="n">
-        <v>0.734883069992065</v>
+        <v>0.734883010387421</v>
       </c>
       <c r="H28" t="n">
         <v>19100</v>
@@ -1268,7 +1268,7 @@
         <v>0.790633022785187</v>
       </c>
       <c r="G31" t="n">
-        <v>0.704428136348724</v>
+        <v>0.70442807674408</v>
       </c>
       <c r="H31" t="n">
         <v>7569</v>
@@ -1355,7 +1355,7 @@
         <v>0.8332359790802</v>
       </c>
       <c r="G34" t="n">
-        <v>0.742385864257812</v>
+        <v>0.742385923862457</v>
       </c>
       <c r="H34" t="n">
         <v>7451</v>
@@ -1558,7 +1558,7 @@
         <v>0.910516023635864</v>
       </c>
       <c r="G41" t="n">
-        <v>0.811239838600159</v>
+        <v>0.811239898204803</v>
       </c>
       <c r="H41" t="n">
         <v>26265</v>
@@ -1587,7 +1587,7 @@
         <v>0.931321978569031</v>
       </c>
       <c r="G42" t="n">
-        <v>0.829777359962463</v>
+        <v>0.829777300357819</v>
       </c>
       <c r="H42" t="n">
         <v>12079</v>
@@ -1616,7 +1616,7 @@
         <v>0.965503990650177</v>
       </c>
       <c r="G43" t="n">
-        <v>0.860232353210449</v>
+        <v>0.860232293605804</v>
       </c>
       <c r="H43" t="n">
         <v>5234</v>
@@ -1761,7 +1761,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G48" t="n">
-        <v>0.85625958442688</v>
+        <v>0.856259524822235</v>
       </c>
       <c r="H48" t="n">
         <v>2604</v>
@@ -1790,7 +1790,7 @@
         <v>0.925378024578094</v>
       </c>
       <c r="G49" t="n">
-        <v>0.82448148727417</v>
+        <v>0.824481427669525</v>
       </c>
       <c r="H49" t="n">
         <v>16427</v>
@@ -1877,7 +1877,7 @@
         <v>0.913488984107971</v>
       </c>
       <c r="G52" t="n">
-        <v>0.813888669013977</v>
+        <v>0.813888728618622</v>
       </c>
       <c r="H52" t="n">
         <v>9147</v>
@@ -1906,7 +1906,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G53" t="n">
-        <v>0.812122821807861</v>
+        <v>0.812122881412506</v>
       </c>
       <c r="H53" t="n">
         <v>5228</v>
@@ -1993,7 +1993,7 @@
         <v>0.9288449883461</v>
       </c>
       <c r="G56" t="n">
-        <v>0.827570378780365</v>
+        <v>0.82757043838501</v>
       </c>
       <c r="H56" t="n">
         <v>15931</v>
@@ -2022,7 +2022,7 @@
         <v>0.931321978569031</v>
       </c>
       <c r="G57" t="n">
-        <v>0.829777359962463</v>
+        <v>0.829777300357819</v>
       </c>
       <c r="H57" t="n">
         <v>15407</v>
@@ -2196,7 +2196,7 @@
         <v>0.95856899023056</v>
       </c>
       <c r="G63" t="n">
-        <v>0.854053556919098</v>
+        <v>0.854053497314453</v>
       </c>
       <c r="H63" t="n">
         <v>17257</v>
@@ -2254,7 +2254,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G65" t="n">
-        <v>0.85625958442688</v>
+        <v>0.856259524822235</v>
       </c>
       <c r="H65" t="n">
         <v>25879</v>
@@ -2283,7 +2283,7 @@
         <v>0.952624022960663</v>
       </c>
       <c r="G66" t="n">
-        <v>0.848756670951843</v>
+        <v>0.848756730556488</v>
       </c>
       <c r="H66" t="n">
         <v>10698</v>
@@ -2399,7 +2399,7 @@
         <v>0.957081973552704</v>
       </c>
       <c r="G70" t="n">
-        <v>0.852728605270386</v>
+        <v>0.852728664875031</v>
       </c>
       <c r="H70" t="n">
         <v>20319</v>
@@ -2544,7 +2544,7 @@
         <v>1.0710209608078</v>
       </c>
       <c r="G75" t="n">
-        <v>0.954244554042816</v>
+        <v>0.954244494438171</v>
       </c>
       <c r="H75" t="n">
         <v>62338</v>
@@ -2776,7 +2776,7 @@
         <v>1.19387602806091</v>
       </c>
       <c r="G83" t="n">
-        <v>1.06370437145233</v>
+        <v>1.06370425224304</v>
       </c>
       <c r="H83" t="n">
         <v>21496</v>
@@ -2805,7 +2805,7 @@
         <v>1.19982099533081</v>
       </c>
       <c r="G84" t="n">
-        <v>1.06900107860565</v>
+        <v>1.06900119781494</v>
       </c>
       <c r="H84" t="n">
         <v>17658</v>
@@ -2834,7 +2834,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G85" t="n">
-        <v>1.08930361270905</v>
+        <v>1.08930349349976</v>
       </c>
       <c r="H85" t="n">
         <v>16563</v>
@@ -2921,7 +2921,7 @@
         <v>1.13938403129578</v>
       </c>
       <c r="G88" t="n">
-        <v>1.01515376567841</v>
+        <v>1.0151538848877</v>
       </c>
       <c r="H88" t="n">
         <v>43542</v>
@@ -3095,7 +3095,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G94" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134198665619</v>
       </c>
       <c r="H94" t="n">
         <v>1518</v>
@@ -3240,7 +3240,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G99" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134198665619</v>
       </c>
       <c r="H99" t="n">
         <v>20985</v>
@@ -3269,7 +3269,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G100" t="n">
-        <v>0.944533944129944</v>
+        <v>0.944534003734589</v>
       </c>
       <c r="H100" t="n">
         <v>12814</v>
@@ -3298,7 +3298,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971015989780426</v>
+        <v>0.971016108989716</v>
       </c>
       <c r="H101" t="n">
         <v>19652</v>
@@ -80038,6 +80038,35 @@
         <v>9621</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.939238011837006</v>
+        <v>0.939237952232361</v>
       </c>
       <c r="H3" t="n">
         <v>17307</v>
@@ -485,7 +485,7 @@
         <v>1.04030704498291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926879465579987</v>
+        <v>0.926879405975342</v>
       </c>
       <c r="H4" t="n">
         <v>6401</v>
@@ -514,7 +514,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.910106956958771</v>
+        <v>0.910106897354126</v>
       </c>
       <c r="H5" t="n">
         <v>44193</v>
@@ -630,7 +630,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910106956958771</v>
+        <v>0.910106897354126</v>
       </c>
       <c r="H9" t="n">
         <v>24329</v>
@@ -659,7 +659,7 @@
         <v>1.02049195766449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.909224808216095</v>
+        <v>0.90922486782074</v>
       </c>
       <c r="H10" t="n">
         <v>2966</v>
@@ -891,7 +891,7 @@
         <v>0.951138019561768</v>
       </c>
       <c r="G18" t="n">
-        <v>0.847432792186737</v>
+        <v>0.847432732582092</v>
       </c>
       <c r="H18" t="n">
         <v>8438</v>
@@ -1007,7 +1007,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G22" t="n">
-        <v>0.856259524822235</v>
+        <v>0.85625958442688</v>
       </c>
       <c r="H22" t="n">
         <v>10047</v>
@@ -1065,7 +1065,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G24" t="n">
-        <v>0.812122881412506</v>
+        <v>0.812122821807861</v>
       </c>
       <c r="H24" t="n">
         <v>12656</v>
@@ -1181,7 +1181,7 @@
         <v>0.824814975261688</v>
       </c>
       <c r="G28" t="n">
-        <v>0.734883010387421</v>
+        <v>0.734883069992065</v>
       </c>
       <c r="H28" t="n">
         <v>19100</v>
@@ -1268,7 +1268,7 @@
         <v>0.790633022785187</v>
       </c>
       <c r="G31" t="n">
-        <v>0.70442807674408</v>
+        <v>0.704428136348724</v>
       </c>
       <c r="H31" t="n">
         <v>7569</v>
@@ -1355,7 +1355,7 @@
         <v>0.8332359790802</v>
       </c>
       <c r="G34" t="n">
-        <v>0.742385923862457</v>
+        <v>0.742385864257812</v>
       </c>
       <c r="H34" t="n">
         <v>7451</v>
@@ -1558,7 +1558,7 @@
         <v>0.910516023635864</v>
       </c>
       <c r="G41" t="n">
-        <v>0.811239898204803</v>
+        <v>0.811239838600159</v>
       </c>
       <c r="H41" t="n">
         <v>26265</v>
@@ -1587,7 +1587,7 @@
         <v>0.931321978569031</v>
       </c>
       <c r="G42" t="n">
-        <v>0.829777300357819</v>
+        <v>0.829777359962463</v>
       </c>
       <c r="H42" t="n">
         <v>12079</v>
@@ -1616,7 +1616,7 @@
         <v>0.965503990650177</v>
       </c>
       <c r="G43" t="n">
-        <v>0.860232293605804</v>
+        <v>0.860232353210449</v>
       </c>
       <c r="H43" t="n">
         <v>5234</v>
@@ -1761,7 +1761,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G48" t="n">
-        <v>0.856259524822235</v>
+        <v>0.85625958442688</v>
       </c>
       <c r="H48" t="n">
         <v>2604</v>
@@ -1790,7 +1790,7 @@
         <v>0.925378024578094</v>
       </c>
       <c r="G49" t="n">
-        <v>0.824481427669525</v>
+        <v>0.82448148727417</v>
       </c>
       <c r="H49" t="n">
         <v>16427</v>
@@ -1877,7 +1877,7 @@
         <v>0.913488984107971</v>
       </c>
       <c r="G52" t="n">
-        <v>0.813888728618622</v>
+        <v>0.813888669013977</v>
       </c>
       <c r="H52" t="n">
         <v>9147</v>
@@ -1906,7 +1906,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G53" t="n">
-        <v>0.812122881412506</v>
+        <v>0.812122821807861</v>
       </c>
       <c r="H53" t="n">
         <v>5228</v>
@@ -1993,7 +1993,7 @@
         <v>0.9288449883461</v>
       </c>
       <c r="G56" t="n">
-        <v>0.82757043838501</v>
+        <v>0.827570378780365</v>
       </c>
       <c r="H56" t="n">
         <v>15931</v>
@@ -2022,7 +2022,7 @@
         <v>0.931321978569031</v>
       </c>
       <c r="G57" t="n">
-        <v>0.829777300357819</v>
+        <v>0.829777359962463</v>
       </c>
       <c r="H57" t="n">
         <v>15407</v>
@@ -2196,7 +2196,7 @@
         <v>0.95856899023056</v>
       </c>
       <c r="G63" t="n">
-        <v>0.854053497314453</v>
+        <v>0.854053556919098</v>
       </c>
       <c r="H63" t="n">
         <v>17257</v>
@@ -2254,7 +2254,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G65" t="n">
-        <v>0.856259524822235</v>
+        <v>0.85625958442688</v>
       </c>
       <c r="H65" t="n">
         <v>25879</v>
@@ -2283,7 +2283,7 @@
         <v>0.952624022960663</v>
       </c>
       <c r="G66" t="n">
-        <v>0.848756730556488</v>
+        <v>0.848756670951843</v>
       </c>
       <c r="H66" t="n">
         <v>10698</v>
@@ -2399,7 +2399,7 @@
         <v>0.957081973552704</v>
       </c>
       <c r="G70" t="n">
-        <v>0.852728664875031</v>
+        <v>0.852728605270386</v>
       </c>
       <c r="H70" t="n">
         <v>20319</v>
@@ -2544,7 +2544,7 @@
         <v>1.0710209608078</v>
       </c>
       <c r="G75" t="n">
-        <v>0.954244494438171</v>
+        <v>0.954244554042816</v>
       </c>
       <c r="H75" t="n">
         <v>62338</v>
@@ -2776,7 +2776,7 @@
         <v>1.19387602806091</v>
       </c>
       <c r="G83" t="n">
-        <v>1.06370425224304</v>
+        <v>1.06370437145233</v>
       </c>
       <c r="H83" t="n">
         <v>21496</v>
@@ -2805,7 +2805,7 @@
         <v>1.19982099533081</v>
       </c>
       <c r="G84" t="n">
-        <v>1.06900119781494</v>
+        <v>1.06900107860565</v>
       </c>
       <c r="H84" t="n">
         <v>17658</v>
@@ -2834,7 +2834,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G85" t="n">
-        <v>1.08930349349976</v>
+        <v>1.08930361270905</v>
       </c>
       <c r="H85" t="n">
         <v>16563</v>
@@ -2921,7 +2921,7 @@
         <v>1.13938403129578</v>
       </c>
       <c r="G88" t="n">
-        <v>1.0151538848877</v>
+        <v>1.01515376567841</v>
       </c>
       <c r="H88" t="n">
         <v>43542</v>
@@ -3095,7 +3095,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G94" t="n">
-        <v>0.970134198665619</v>
+        <v>0.970134079456329</v>
       </c>
       <c r="H94" t="n">
         <v>1518</v>
@@ -3240,7 +3240,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G99" t="n">
-        <v>0.970134198665619</v>
+        <v>0.970134079456329</v>
       </c>
       <c r="H99" t="n">
         <v>20985</v>
@@ -3269,7 +3269,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G100" t="n">
-        <v>0.944534003734589</v>
+        <v>0.944533944129944</v>
       </c>
       <c r="H100" t="n">
         <v>12814</v>
@@ -3298,7 +3298,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971016108989716</v>
+        <v>0.971015989780426</v>
       </c>
       <c r="H101" t="n">
         <v>19652</v>
@@ -80067,6 +80067,35 @@
         <v>0</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.05913197994232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.943651854991913</v>
+        <v>0.943651795387268</v>
       </c>
       <c r="H2" t="n">
         <v>13804</v>
@@ -456,7 +456,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.939237952232361</v>
+        <v>0.939238011837006</v>
       </c>
       <c r="H3" t="n">
         <v>17307</v>
@@ -543,7 +543,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G6" t="n">
-        <v>0.891569495201111</v>
+        <v>0.891569435596466</v>
       </c>
       <c r="H6" t="n">
         <v>7493</v>
@@ -804,7 +804,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G15" t="n">
-        <v>0.882742643356323</v>
+        <v>0.882742702960968</v>
       </c>
       <c r="H15" t="n">
         <v>17895</v>
@@ -833,7 +833,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G16" t="n">
-        <v>0.891569495201111</v>
+        <v>0.891569435596466</v>
       </c>
       <c r="H16" t="n">
         <v>14859</v>
@@ -949,7 +949,7 @@
         <v>0.968972027301788</v>
       </c>
       <c r="G20" t="n">
-        <v>0.86332231760025</v>
+        <v>0.863322257995605</v>
       </c>
       <c r="H20" t="n">
         <v>1418</v>
@@ -1123,7 +1123,7 @@
         <v>0.870885014533997</v>
       </c>
       <c r="G26" t="n">
-        <v>0.775929987430573</v>
+        <v>0.775929927825928</v>
       </c>
       <c r="H26" t="n">
         <v>26138</v>
@@ -1210,7 +1210,7 @@
         <v>0.812430024147034</v>
       </c>
       <c r="G29" t="n">
-        <v>0.723848521709442</v>
+        <v>0.723848462104797</v>
       </c>
       <c r="H29" t="n">
         <v>38859</v>
@@ -1239,7 +1239,7 @@
         <v>0.76834100484848</v>
       </c>
       <c r="G30" t="n">
-        <v>0.684566617012024</v>
+        <v>0.684566557407379</v>
       </c>
       <c r="H30" t="n">
         <v>30726</v>
@@ -1268,7 +1268,7 @@
         <v>0.790633022785187</v>
       </c>
       <c r="G31" t="n">
-        <v>0.704428136348724</v>
+        <v>0.704428017139435</v>
       </c>
       <c r="H31" t="n">
         <v>7569</v>
@@ -1355,7 +1355,7 @@
         <v>0.8332359790802</v>
       </c>
       <c r="G34" t="n">
-        <v>0.742385864257812</v>
+        <v>0.742385923862457</v>
       </c>
       <c r="H34" t="n">
         <v>7451</v>
@@ -1500,7 +1500,7 @@
         <v>0.837198972702026</v>
       </c>
       <c r="G39" t="n">
-        <v>0.745916783809662</v>
+        <v>0.745916843414307</v>
       </c>
       <c r="H39" t="n">
         <v>26934</v>
@@ -1558,7 +1558,7 @@
         <v>0.910516023635864</v>
       </c>
       <c r="G41" t="n">
-        <v>0.811239838600159</v>
+        <v>0.811239898204803</v>
       </c>
       <c r="H41" t="n">
         <v>26265</v>
@@ -1616,7 +1616,7 @@
         <v>0.965503990650177</v>
       </c>
       <c r="G43" t="n">
-        <v>0.860232353210449</v>
+        <v>0.860232412815094</v>
       </c>
       <c r="H43" t="n">
         <v>5234</v>
@@ -1703,7 +1703,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G46" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H46" t="n">
         <v>5147</v>
@@ -1732,7 +1732,7 @@
         <v>0.946183979511261</v>
       </c>
       <c r="G47" t="n">
-        <v>0.843018889427185</v>
+        <v>0.84301882982254</v>
       </c>
       <c r="H47" t="n">
         <v>9568</v>
@@ -1790,7 +1790,7 @@
         <v>0.925378024578094</v>
       </c>
       <c r="G49" t="n">
-        <v>0.82448148727417</v>
+        <v>0.824481427669525</v>
       </c>
       <c r="H49" t="n">
         <v>16427</v>
@@ -1819,7 +1819,7 @@
         <v>0.924881994724274</v>
       </c>
       <c r="G50" t="n">
-        <v>0.824039459228516</v>
+        <v>0.82403951883316</v>
       </c>
       <c r="H50" t="n">
         <v>7700</v>
@@ -1877,7 +1877,7 @@
         <v>0.913488984107971</v>
       </c>
       <c r="G52" t="n">
-        <v>0.813888669013977</v>
+        <v>0.813888728618622</v>
       </c>
       <c r="H52" t="n">
         <v>9147</v>
@@ -2051,7 +2051,7 @@
         <v>0.933304011821747</v>
       </c>
       <c r="G58" t="n">
-        <v>0.831543207168579</v>
+        <v>0.831543266773224</v>
       </c>
       <c r="H58" t="n">
         <v>5080</v>
@@ -2080,7 +2080,7 @@
         <v>0.933304011821747</v>
       </c>
       <c r="G59" t="n">
-        <v>0.831543207168579</v>
+        <v>0.831543266773224</v>
       </c>
       <c r="H59" t="n">
         <v>14431</v>
@@ -2138,7 +2138,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G61" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H61" t="n">
         <v>25097</v>
@@ -2283,7 +2283,7 @@
         <v>0.952624022960663</v>
       </c>
       <c r="G66" t="n">
-        <v>0.848756670951843</v>
+        <v>0.848756730556488</v>
       </c>
       <c r="H66" t="n">
         <v>10698</v>
@@ -2312,7 +2312,7 @@
         <v>0.971943974494934</v>
       </c>
       <c r="G67" t="n">
-        <v>0.865970134735107</v>
+        <v>0.865970194339752</v>
       </c>
       <c r="H67" t="n">
         <v>10093</v>
@@ -2341,7 +2341,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G68" t="n">
-        <v>0.838604986667633</v>
+        <v>0.838605046272278</v>
       </c>
       <c r="H68" t="n">
         <v>18109</v>
@@ -2486,7 +2486,7 @@
         <v>1.01652801036835</v>
       </c>
       <c r="G73" t="n">
-        <v>0.905693054199219</v>
+        <v>0.905693113803864</v>
       </c>
       <c r="H73" t="n">
         <v>22149</v>
@@ -2515,7 +2515,7 @@
         <v>1.05814099311829</v>
       </c>
       <c r="G74" t="n">
-        <v>0.94276887178421</v>
+        <v>0.942768931388855</v>
       </c>
       <c r="H74" t="n">
         <v>43122</v>
@@ -2573,7 +2573,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G76" t="n">
-        <v>0.986905634403229</v>
+        <v>0.986905694007874</v>
       </c>
       <c r="H76" t="n">
         <v>69226</v>
@@ -2602,7 +2602,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G77" t="n">
-        <v>0.997498393058777</v>
+        <v>0.997498333454132</v>
       </c>
       <c r="H77" t="n">
         <v>75982</v>
@@ -2631,7 +2631,7 @@
         <v>1.18595004081726</v>
       </c>
       <c r="G78" t="n">
-        <v>1.05664265155792</v>
+        <v>1.05664253234863</v>
       </c>
       <c r="H78" t="n">
         <v>93047</v>
@@ -2689,7 +2689,7 @@
         <v>1.15919899940491</v>
       </c>
       <c r="G80" t="n">
-        <v>1.03280830383301</v>
+        <v>1.03280818462372</v>
       </c>
       <c r="H80" t="n">
         <v>19303</v>
@@ -2805,7 +2805,7 @@
         <v>1.19982099533081</v>
       </c>
       <c r="G84" t="n">
-        <v>1.06900107860565</v>
+        <v>1.06900119781494</v>
       </c>
       <c r="H84" t="n">
         <v>17658</v>
@@ -2834,7 +2834,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G85" t="n">
-        <v>1.08930361270905</v>
+        <v>1.08930349349976</v>
       </c>
       <c r="H85" t="n">
         <v>16563</v>
@@ -2950,7 +2950,7 @@
         <v>1.13641202449799</v>
       </c>
       <c r="G89" t="n">
-        <v>1.01250576972961</v>
+        <v>1.0125058889389</v>
       </c>
       <c r="H89" t="n">
         <v>15210</v>
@@ -3037,7 +3037,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G92" t="n">
-        <v>0.986905634403229</v>
+        <v>0.986905694007874</v>
       </c>
       <c r="H92" t="n">
         <v>21899</v>
@@ -3066,7 +3066,7 @@
         <v>1.10569798946381</v>
       </c>
       <c r="G93" t="n">
-        <v>0.985140681266785</v>
+        <v>0.98514062166214</v>
       </c>
       <c r="H93" t="n">
         <v>45101</v>
@@ -3124,7 +3124,7 @@
         <v>1.07795596122742</v>
       </c>
       <c r="G95" t="n">
-        <v>0.960423350334167</v>
+        <v>0.960423409938812</v>
       </c>
       <c r="H95" t="n">
         <v>45454</v>
@@ -3153,7 +3153,7 @@
         <v>1.09975302219391</v>
       </c>
       <c r="G96" t="n">
-        <v>0.979843854904175</v>
+        <v>0.97984379529953</v>
       </c>
       <c r="H96" t="n">
         <v>2018</v>
@@ -3182,7 +3182,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G97" t="n">
-        <v>0.981609702110291</v>
+        <v>0.981609761714935</v>
       </c>
       <c r="H97" t="n">
         <v>54279</v>
@@ -3211,7 +3211,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G98" t="n">
-        <v>0.981609702110291</v>
+        <v>0.981609761714935</v>
       </c>
       <c r="H98" t="n">
         <v>7938</v>
@@ -3269,7 +3269,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G100" t="n">
-        <v>0.944533944129944</v>
+        <v>0.944533884525299</v>
       </c>
       <c r="H100" t="n">
         <v>12814</v>
@@ -3298,7 +3298,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971015989780426</v>
+        <v>0.971016049385071</v>
       </c>
       <c r="H101" t="n">
         <v>19652</v>
@@ -3327,7 +3327,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G102" t="n">
-        <v>0.997498393058777</v>
+        <v>0.997498333454132</v>
       </c>
       <c r="H102" t="n">
         <v>21901</v>
@@ -3385,7 +3385,7 @@
         <v>1.11758697032928</v>
       </c>
       <c r="G104" t="n">
-        <v>0.995733201503754</v>
+        <v>0.995733380317688</v>
       </c>
       <c r="H104" t="n">
         <v>10358</v>
@@ -3443,7 +3443,7 @@
         <v>1.13443005084991</v>
       </c>
       <c r="G106" t="n">
-        <v>1.0107399225235</v>
+        <v>1.01074004173279</v>
       </c>
       <c r="H106" t="n">
         <v>17337</v>
@@ -3588,7 +3588,7 @@
         <v>1.12947595119476</v>
       </c>
       <c r="G111" t="n">
-        <v>1.05007898807526</v>
+        <v>1.05007886886597</v>
       </c>
       <c r="H111" t="n">
         <v>19102</v>
@@ -3646,7 +3646,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G113" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H113" t="n">
         <v>29366</v>
@@ -3675,7 +3675,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G114" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H114" t="n">
         <v>77975</v>
@@ -3733,7 +3733,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G116" t="n">
-        <v>0.953360855579376</v>
+        <v>0.953360915184021</v>
       </c>
       <c r="H116" t="n">
         <v>15611</v>
@@ -3762,7 +3762,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G117" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H117" t="n">
         <v>9790</v>
@@ -3849,7 +3849,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G120" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H120" t="n">
         <v>8326</v>
@@ -3907,7 +3907,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G122" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H122" t="n">
         <v>4774</v>
@@ -3965,7 +3965,7 @@
         <v>0.989777982234955</v>
       </c>
       <c r="G124" t="n">
-        <v>0.920201063156128</v>
+        <v>0.920201122760773</v>
       </c>
       <c r="H124" t="n">
         <v>90762</v>
@@ -4400,7 +4400,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G139" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H139" t="n">
         <v>15649</v>
@@ -4516,7 +4516,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G143" t="n">
-        <v>0.95244038105011</v>
+        <v>0.952440440654755</v>
       </c>
       <c r="H143" t="n">
         <v>8705</v>
@@ -4545,7 +4545,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G144" t="n">
-        <v>0.944150328636169</v>
+        <v>0.944150269031525</v>
       </c>
       <c r="H144" t="n">
         <v>8451</v>
@@ -4951,7 +4951,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G158" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H158" t="n">
         <v>8684</v>
@@ -4980,7 +4980,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G159" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H159" t="n">
         <v>25293</v>
@@ -5067,7 +5067,7 @@
         <v>1.03931605815887</v>
       </c>
       <c r="G162" t="n">
-        <v>0.96625691652298</v>
+        <v>0.966256856918335</v>
       </c>
       <c r="H162" t="n">
         <v>4037</v>
@@ -5125,7 +5125,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G164" t="n">
-        <v>0.959809303283691</v>
+        <v>0.959809362888336</v>
       </c>
       <c r="H164" t="n">
         <v>4758</v>
@@ -5154,7 +5154,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G165" t="n">
-        <v>0.95244038105011</v>
+        <v>0.952440440654755</v>
       </c>
       <c r="H165" t="n">
         <v>6186</v>
@@ -5241,7 +5241,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G168" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H168" t="n">
         <v>26716</v>
@@ -5357,7 +5357,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G172" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H172" t="n">
         <v>5069</v>
@@ -5560,7 +5560,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G179" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H179" t="n">
         <v>8029</v>
@@ -5618,7 +5618,7 @@
         <v>1.09876203536987</v>
       </c>
       <c r="G181" t="n">
-        <v>1.02152407169342</v>
+        <v>1.02152395248413</v>
       </c>
       <c r="H181" t="n">
         <v>18375</v>
@@ -5879,7 +5879,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G190" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H190" t="n">
         <v>25435</v>
@@ -5937,7 +5937,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G192" t="n">
-        <v>0.986521542072296</v>
+        <v>0.986521601676941</v>
       </c>
       <c r="H192" t="n">
         <v>2493</v>
@@ -5966,7 +5966,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G193" t="n">
-        <v>0.971783936023712</v>
+        <v>0.971783995628357</v>
       </c>
       <c r="H193" t="n">
         <v>1211</v>
@@ -5995,7 +5995,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G194" t="n">
-        <v>0.993890404701233</v>
+        <v>0.993890345096588</v>
       </c>
       <c r="H194" t="n">
         <v>5778</v>
@@ -6169,7 +6169,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G200" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H200" t="n">
         <v>4188</v>
@@ -6227,7 +6227,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G202" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H202" t="n">
         <v>4028</v>
@@ -6256,7 +6256,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G203" t="n">
-        <v>0.964415073394775</v>
+        <v>0.96441513299942</v>
       </c>
       <c r="H203" t="n">
         <v>596</v>
@@ -6285,7 +6285,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G204" t="n">
-        <v>0.964415073394775</v>
+        <v>0.96441513299942</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>1.04129803180695</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968099534511566</v>
+        <v>0.968099474906921</v>
       </c>
       <c r="H205" t="n">
         <v>14297</v>
@@ -6343,7 +6343,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G206" t="n">
-        <v>0.971783936023712</v>
+        <v>0.971783995628357</v>
       </c>
       <c r="H206" t="n">
         <v>1110</v>
@@ -6372,7 +6372,7 @@
         <v>1.05318701267242</v>
       </c>
       <c r="G207" t="n">
-        <v>0.979152798652649</v>
+        <v>0.979152739048004</v>
       </c>
       <c r="H207" t="n">
         <v>7791</v>
@@ -6401,7 +6401,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G208" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H208" t="n">
         <v>11810</v>
@@ -6430,7 +6430,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G209" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H209" t="n">
         <v>10194</v>
@@ -6459,7 +6459,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G210" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H210" t="n">
         <v>9285</v>
@@ -6488,7 +6488,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G211" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H211" t="n">
         <v>14863</v>
@@ -6517,7 +6517,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G212" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H212" t="n">
         <v>9225</v>
@@ -6546,7 +6546,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G213" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H213" t="n">
         <v>6810</v>
@@ -6604,7 +6604,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G215" t="n">
-        <v>0.980074048042297</v>
+        <v>0.980074107646942</v>
       </c>
       <c r="H215" t="n">
         <v>13653</v>
@@ -6633,7 +6633,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G216" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H216" t="n">
         <v>8511</v>
@@ -6662,7 +6662,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G217" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H217" t="n">
         <v>1379</v>
@@ -6691,7 +6691,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G218" t="n">
-        <v>0.969019889831543</v>
+        <v>0.969019830226898</v>
       </c>
       <c r="H218" t="n">
         <v>6626</v>
@@ -6720,7 +6720,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G219" t="n">
-        <v>0.969019889831543</v>
+        <v>0.969019830226898</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.01850998401642</v>
       </c>
       <c r="G223" t="n">
-        <v>0.946913361549377</v>
+        <v>0.946913421154022</v>
       </c>
       <c r="H223" t="n">
         <v>14159</v>
@@ -6894,7 +6894,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G225" t="n">
-        <v>0.944150328636169</v>
+        <v>0.944150269031525</v>
       </c>
       <c r="H225" t="n">
         <v>2501</v>
@@ -6952,7 +6952,7 @@
         <v>1.01256501674652</v>
       </c>
       <c r="G227" t="n">
-        <v>0.941386342048645</v>
+        <v>0.941386282444</v>
       </c>
       <c r="H227" t="n">
         <v>3071</v>
@@ -6981,7 +6981,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G228" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H228" t="n">
         <v>11372</v>
@@ -7010,7 +7010,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G229" t="n">
-        <v>0.930333077907562</v>
+        <v>0.930333018302917</v>
       </c>
       <c r="H229" t="n">
         <v>18001</v>
@@ -7039,7 +7039,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G230" t="n">
-        <v>0.921122431755066</v>
+        <v>0.921122491359711</v>
       </c>
       <c r="H230" t="n">
         <v>8579</v>
@@ -7068,7 +7068,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G231" t="n">
-        <v>0.908226490020752</v>
+        <v>0.908226549625397</v>
       </c>
       <c r="H231" t="n">
         <v>19373</v>
@@ -7097,7 +7097,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G232" t="n">
-        <v>0.908226490020752</v>
+        <v>0.908226549625397</v>
       </c>
       <c r="H232" t="n">
         <v>3324</v>
@@ -7155,7 +7155,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G234" t="n">
-        <v>0.921122431755066</v>
+        <v>0.921122491359711</v>
       </c>
       <c r="H234" t="n">
         <v>17158</v>
@@ -7358,7 +7358,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G241" t="n">
-        <v>0.953360855579376</v>
+        <v>0.953360915184021</v>
       </c>
       <c r="H241" t="n">
         <v>15341</v>
@@ -7532,7 +7532,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G247" t="n">
-        <v>0.959809303283691</v>
+        <v>0.959809362888336</v>
       </c>
       <c r="H247" t="n">
         <v>10361</v>
@@ -7590,7 +7590,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G249" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H249" t="n">
         <v>73427</v>
@@ -7619,7 +7619,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G250" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H250" t="n">
         <v>13479</v>
@@ -7648,7 +7648,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G251" t="n">
-        <v>0.98283714056015</v>
+        <v>0.982837200164795</v>
       </c>
       <c r="H251" t="n">
         <v>36869</v>
@@ -7677,7 +7677,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G252" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H252" t="n">
         <v>4734</v>
@@ -7706,7 +7706,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G253" t="n">
-        <v>0.963493764400482</v>
+        <v>0.963493824005127</v>
       </c>
       <c r="H253" t="n">
         <v>12686</v>
@@ -7793,7 +7793,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G256" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H256" t="n">
         <v>2465</v>
@@ -7909,7 +7909,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G260" t="n">
-        <v>0.986521542072296</v>
+        <v>0.986521601676941</v>
       </c>
       <c r="H260" t="n">
         <v>12963</v>
@@ -8025,7 +8025,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G264" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H264" t="n">
         <v>18431</v>
@@ -8199,7 +8199,7 @@
         <v>1.09182703495026</v>
       </c>
       <c r="G270" t="n">
-        <v>1.01507663726807</v>
+        <v>1.01507651805878</v>
       </c>
       <c r="H270" t="n">
         <v>5995</v>
@@ -8286,7 +8286,7 @@
         <v>1.1086699962616</v>
       </c>
       <c r="G273" t="n">
-        <v>1.03073561191559</v>
+        <v>1.0307354927063</v>
       </c>
       <c r="H273" t="n">
         <v>17630</v>
@@ -8373,7 +8373,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G276" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H276" t="n">
         <v>9941</v>
@@ -8460,7 +8460,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G279" t="n">
-        <v>0.996654391288757</v>
+        <v>0.996654331684113</v>
       </c>
       <c r="H279" t="n">
         <v>504</v>
@@ -8547,7 +8547,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G282" t="n">
-        <v>0.994811773300171</v>
+        <v>0.994811713695526</v>
       </c>
       <c r="H282" t="n">
         <v>2869</v>
@@ -8576,7 +8576,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G283" t="n">
-        <v>0.975468397140503</v>
+        <v>0.975468277931213</v>
       </c>
       <c r="H283" t="n">
         <v>201</v>
@@ -8605,7 +8605,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G284" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H284" t="n">
         <v>19922</v>
@@ -8634,7 +8634,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G285" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H285" t="n">
         <v>6055</v>
@@ -8663,7 +8663,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G286" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H286" t="n">
         <v>4022</v>
@@ -8692,7 +8692,7 @@
         <v>1.06210398674011</v>
       </c>
       <c r="G287" t="n">
-        <v>0.987442910671234</v>
+        <v>0.987442851066589</v>
       </c>
       <c r="H287" t="n">
         <v>5271</v>
@@ -8721,7 +8721,7 @@
         <v>1.0650759935379</v>
       </c>
       <c r="G288" t="n">
-        <v>0.990205943584442</v>
+        <v>0.990206062793732</v>
       </c>
       <c r="H288" t="n">
         <v>23250</v>
@@ -8750,7 +8750,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G289" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H289" t="n">
         <v>11556</v>
@@ -8779,7 +8779,7 @@
         <v>1.05615901947021</v>
       </c>
       <c r="G290" t="n">
-        <v>0.981915891170502</v>
+        <v>0.981915831565857</v>
       </c>
       <c r="H290" t="n">
         <v>2424</v>
@@ -8808,7 +8808,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G291" t="n">
-        <v>0.985600292682648</v>
+        <v>0.985600233078003</v>
       </c>
       <c r="H291" t="n">
         <v>5183</v>
@@ -8837,7 +8837,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G292" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H292" t="n">
         <v>2704</v>
@@ -8866,7 +8866,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G293" t="n">
-        <v>0.999417424201965</v>
+        <v>0.999417543411255</v>
       </c>
       <c r="H293" t="n">
         <v>630</v>
@@ -8953,7 +8953,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G296" t="n">
-        <v>0.992969155311584</v>
+        <v>0.99296909570694</v>
       </c>
       <c r="H296" t="n">
         <v>413</v>
@@ -9011,7 +9011,7 @@
         <v>1.11263298988342</v>
       </c>
       <c r="G298" t="n">
-        <v>1.03442001342773</v>
+        <v>1.03441989421844</v>
       </c>
       <c r="H298" t="n">
         <v>10092</v>
@@ -9185,7 +9185,7 @@
         <v>1.21270096302032</v>
       </c>
       <c r="G304" t="n">
-        <v>1.12745356559753</v>
+        <v>1.12745368480682</v>
       </c>
       <c r="H304" t="n">
         <v>345383</v>
@@ -9272,7 +9272,7 @@
         <v>1.16613495349884</v>
       </c>
       <c r="G307" t="n">
-        <v>1.08416092395782</v>
+        <v>1.08416104316711</v>
       </c>
       <c r="H307" t="n">
         <v>147608</v>
@@ -9330,7 +9330,7 @@
         <v>1.17802405357361</v>
       </c>
       <c r="G309" t="n">
-        <v>1.09521436691284</v>
+        <v>1.09521424770355</v>
       </c>
       <c r="H309" t="n">
         <v>32265</v>
@@ -9359,7 +9359,7 @@
         <v>1.1869410276413</v>
       </c>
       <c r="G310" t="n">
-        <v>1.10350453853607</v>
+        <v>1.10350441932678</v>
       </c>
       <c r="H310" t="n">
         <v>4885</v>
@@ -9504,7 +9504,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G315" t="n">
-        <v>1.13666427135468</v>
+        <v>1.13666415214539</v>
       </c>
       <c r="H315" t="n">
         <v>59543</v>
@@ -9533,7 +9533,7 @@
         <v>1.21864497661591</v>
       </c>
       <c r="G316" t="n">
-        <v>1.13297986984253</v>
+        <v>1.13297975063324</v>
       </c>
       <c r="H316" t="n">
         <v>100407</v>
@@ -9591,7 +9591,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G318" t="n">
-        <v>1.13666427135468</v>
+        <v>1.13666415214539</v>
       </c>
       <c r="H318" t="n">
         <v>22044</v>
@@ -9736,7 +9736,7 @@
         <v>1.31673204898834</v>
       </c>
       <c r="G323" t="n">
-        <v>1.22417187690735</v>
+        <v>1.22417175769806</v>
       </c>
       <c r="H323" t="n">
         <v>194343</v>
@@ -9852,7 +9852,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G327" t="n">
-        <v>1.1799578666687</v>
+        <v>1.17995774745941</v>
       </c>
       <c r="H327" t="n">
         <v>102280</v>
@@ -9939,7 +9939,7 @@
         <v>1.29889798164368</v>
       </c>
       <c r="G330" t="n">
-        <v>1.2075914144516</v>
+        <v>1.20759129524231</v>
       </c>
       <c r="H330" t="n">
         <v>47401</v>
@@ -9968,7 +9968,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G331" t="n">
-        <v>1.16521918773651</v>
+        <v>1.16521906852722</v>
       </c>
       <c r="H331" t="n">
         <v>142707</v>
@@ -10200,7 +10200,7 @@
         <v>1.22954404354095</v>
       </c>
       <c r="G339" t="n">
-        <v>1.14311265945435</v>
+        <v>1.14311277866364</v>
       </c>
       <c r="H339" t="n">
         <v>15944</v>
@@ -10287,7 +10287,7 @@
         <v>1.19783902168274</v>
       </c>
       <c r="G342" t="n">
-        <v>1.11363649368286</v>
+        <v>1.11363637447357</v>
       </c>
       <c r="H342" t="n">
         <v>10206</v>
@@ -10316,7 +10316,7 @@
         <v>1.19585800170898</v>
       </c>
       <c r="G343" t="n">
-        <v>1.11179459095001</v>
+        <v>1.1117947101593</v>
       </c>
       <c r="H343" t="n">
         <v>48580</v>
@@ -10345,7 +10345,7 @@
         <v>1.20378398895264</v>
       </c>
       <c r="G344" t="n">
-        <v>1.11916351318359</v>
+        <v>1.1191633939743</v>
       </c>
       <c r="H344" t="n">
         <v>24146</v>
@@ -10374,7 +10374,7 @@
         <v>1.22657203674316</v>
       </c>
       <c r="G345" t="n">
-        <v>1.14034962654114</v>
+        <v>1.14034950733185</v>
       </c>
       <c r="H345" t="n">
         <v>16104</v>
@@ -10461,7 +10461,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G348" t="n">
-        <v>1.16521918773651</v>
+        <v>1.16521906852722</v>
       </c>
       <c r="H348" t="n">
         <v>32469</v>
@@ -10519,7 +10519,7 @@
         <v>1.31375896930695</v>
       </c>
       <c r="G350" t="n">
-        <v>1.22140777111053</v>
+        <v>1.22140765190125</v>
       </c>
       <c r="H350" t="n">
         <v>171747</v>
@@ -10606,7 +10606,7 @@
         <v>1.26719295978546</v>
       </c>
       <c r="G353" t="n">
-        <v>1.17811512947083</v>
+        <v>1.17811501026154</v>
       </c>
       <c r="H353" t="n">
         <v>40097</v>
@@ -10635,7 +10635,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G354" t="n">
-        <v>1.1799578666687</v>
+        <v>1.17995774745941</v>
       </c>
       <c r="H354" t="n">
         <v>25472</v>
@@ -10809,7 +10809,7 @@
         <v>1.35834395885468</v>
       </c>
       <c r="G360" t="n">
-        <v>1.26285862922668</v>
+        <v>1.2628585100174</v>
       </c>
       <c r="H360" t="n">
         <v>4290</v>
@@ -80096,6 +80096,35 @@
         <v>0</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.05913197994232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.943651795387268</v>
+        <v>0.943651854991913</v>
       </c>
       <c r="H2" t="n">
         <v>13804</v>
@@ -485,7 +485,7 @@
         <v>1.04030704498291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926879405975342</v>
+        <v>0.926879465579987</v>
       </c>
       <c r="H4" t="n">
         <v>6401</v>
@@ -514,7 +514,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H5" t="n">
         <v>44193</v>
@@ -543,7 +543,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G6" t="n">
-        <v>0.891569435596466</v>
+        <v>0.891569495201111</v>
       </c>
       <c r="H6" t="n">
         <v>7493</v>
@@ -601,7 +601,7 @@
         <v>1.01058399677277</v>
       </c>
       <c r="G8" t="n">
-        <v>0.900397121906281</v>
+        <v>0.900397181510925</v>
       </c>
       <c r="H8" t="n">
         <v>23254</v>
@@ -630,7 +630,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H9" t="n">
         <v>24329</v>
@@ -659,7 +659,7 @@
         <v>1.02049195766449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.90922486782074</v>
+        <v>0.909224808216095</v>
       </c>
       <c r="H10" t="n">
         <v>2966</v>
@@ -688,7 +688,7 @@
         <v>0.998695015907288</v>
       </c>
       <c r="G11" t="n">
-        <v>0.889804482460022</v>
+        <v>0.889804422855377</v>
       </c>
       <c r="H11" t="n">
         <v>63536</v>
@@ -833,7 +833,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G16" t="n">
-        <v>0.891569435596466</v>
+        <v>0.891569495201111</v>
       </c>
       <c r="H16" t="n">
         <v>14859</v>
@@ -891,7 +891,7 @@
         <v>0.951138019561768</v>
       </c>
       <c r="G18" t="n">
-        <v>0.847432732582092</v>
+        <v>0.847432792186737</v>
       </c>
       <c r="H18" t="n">
         <v>8438</v>
@@ -920,7 +920,7 @@
         <v>0.970457971096039</v>
       </c>
       <c r="G19" t="n">
-        <v>0.864646196365356</v>
+        <v>0.864646255970001</v>
       </c>
       <c r="H19" t="n">
         <v>3784</v>
@@ -1123,7 +1123,7 @@
         <v>0.870885014533997</v>
       </c>
       <c r="G26" t="n">
-        <v>0.775929927825928</v>
+        <v>0.775929987430573</v>
       </c>
       <c r="H26" t="n">
         <v>26138</v>
@@ -1210,7 +1210,7 @@
         <v>0.812430024147034</v>
       </c>
       <c r="G29" t="n">
-        <v>0.723848462104797</v>
+        <v>0.723848521709442</v>
       </c>
       <c r="H29" t="n">
         <v>38859</v>
@@ -1239,7 +1239,7 @@
         <v>0.76834100484848</v>
       </c>
       <c r="G30" t="n">
-        <v>0.684566557407379</v>
+        <v>0.684566617012024</v>
       </c>
       <c r="H30" t="n">
         <v>30726</v>
@@ -1268,7 +1268,7 @@
         <v>0.790633022785187</v>
       </c>
       <c r="G31" t="n">
-        <v>0.704428017139435</v>
+        <v>0.70442807674408</v>
       </c>
       <c r="H31" t="n">
         <v>7569</v>
@@ -1355,7 +1355,7 @@
         <v>0.8332359790802</v>
       </c>
       <c r="G34" t="n">
-        <v>0.742385923862457</v>
+        <v>0.742385864257812</v>
       </c>
       <c r="H34" t="n">
         <v>7451</v>
@@ -1500,7 +1500,7 @@
         <v>0.837198972702026</v>
       </c>
       <c r="G39" t="n">
-        <v>0.745916843414307</v>
+        <v>0.745916783809662</v>
       </c>
       <c r="H39" t="n">
         <v>26934</v>
@@ -1703,7 +1703,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G46" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H46" t="n">
         <v>5147</v>
@@ -1790,7 +1790,7 @@
         <v>0.925378024578094</v>
       </c>
       <c r="G49" t="n">
-        <v>0.824481427669525</v>
+        <v>0.82448148727417</v>
       </c>
       <c r="H49" t="n">
         <v>16427</v>
@@ -1848,7 +1848,7 @@
         <v>0.920423984527588</v>
       </c>
       <c r="G51" t="n">
-        <v>0.820067584514618</v>
+        <v>0.820067524909973</v>
       </c>
       <c r="H51" t="n">
         <v>5213</v>
@@ -1877,7 +1877,7 @@
         <v>0.913488984107971</v>
       </c>
       <c r="G52" t="n">
-        <v>0.813888728618622</v>
+        <v>0.813888669013977</v>
       </c>
       <c r="H52" t="n">
         <v>9147</v>
@@ -2051,7 +2051,7 @@
         <v>0.933304011821747</v>
       </c>
       <c r="G58" t="n">
-        <v>0.831543266773224</v>
+        <v>0.831543207168579</v>
       </c>
       <c r="H58" t="n">
         <v>5080</v>
@@ -2080,7 +2080,7 @@
         <v>0.933304011821747</v>
       </c>
       <c r="G59" t="n">
-        <v>0.831543266773224</v>
+        <v>0.831543207168579</v>
       </c>
       <c r="H59" t="n">
         <v>14431</v>
@@ -2109,7 +2109,7 @@
         <v>0.935781002044678</v>
       </c>
       <c r="G60" t="n">
-        <v>0.833750188350677</v>
+        <v>0.833750128746033</v>
       </c>
       <c r="H60" t="n">
         <v>4464</v>
@@ -2138,7 +2138,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G61" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H61" t="n">
         <v>25097</v>
@@ -2196,7 +2196,7 @@
         <v>0.95856899023056</v>
       </c>
       <c r="G63" t="n">
-        <v>0.854053556919098</v>
+        <v>0.854053497314453</v>
       </c>
       <c r="H63" t="n">
         <v>17257</v>
@@ -2341,7 +2341,7 @@
         <v>0.941229999065399</v>
       </c>
       <c r="G68" t="n">
-        <v>0.838605046272278</v>
+        <v>0.838604986667633</v>
       </c>
       <c r="H68" t="n">
         <v>18109</v>
@@ -2399,7 +2399,7 @@
         <v>0.957081973552704</v>
       </c>
       <c r="G70" t="n">
-        <v>0.852728605270386</v>
+        <v>0.852728664875031</v>
       </c>
       <c r="H70" t="n">
         <v>20319</v>
@@ -2428,7 +2428,7 @@
         <v>0.979870021343231</v>
       </c>
       <c r="G71" t="n">
-        <v>0.873032033443451</v>
+        <v>0.873031973838806</v>
       </c>
       <c r="H71" t="n">
         <v>1148</v>
@@ -2689,7 +2689,7 @@
         <v>1.15919899940491</v>
       </c>
       <c r="G80" t="n">
-        <v>1.03280818462372</v>
+        <v>1.03280830383301</v>
       </c>
       <c r="H80" t="n">
         <v>19303</v>
@@ -2718,7 +2718,7 @@
         <v>1.1274950504303</v>
       </c>
       <c r="G81" t="n">
-        <v>1.0045610666275</v>
+        <v>1.00456094741821</v>
       </c>
       <c r="H81" t="n">
         <v>21319</v>
@@ -2863,7 +2863,7 @@
         <v>1.16018998622894</v>
       </c>
       <c r="G86" t="n">
-        <v>1.03369116783142</v>
+        <v>1.03369128704071</v>
       </c>
       <c r="H86" t="n">
         <v>35930</v>
@@ -3095,7 +3095,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G94" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134019851685</v>
       </c>
       <c r="H94" t="n">
         <v>1518</v>
@@ -3153,7 +3153,7 @@
         <v>1.09975302219391</v>
       </c>
       <c r="G96" t="n">
-        <v>0.97984379529953</v>
+        <v>0.979843854904175</v>
       </c>
       <c r="H96" t="n">
         <v>2018</v>
@@ -3182,7 +3182,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G97" t="n">
-        <v>0.981609761714935</v>
+        <v>0.981609702110291</v>
       </c>
       <c r="H97" t="n">
         <v>54279</v>
@@ -3211,7 +3211,7 @@
         <v>1.10173499584198</v>
       </c>
       <c r="G98" t="n">
-        <v>0.981609761714935</v>
+        <v>0.981609702110291</v>
       </c>
       <c r="H98" t="n">
         <v>7938</v>
@@ -3240,7 +3240,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G99" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134019851685</v>
       </c>
       <c r="H99" t="n">
         <v>20985</v>
@@ -3298,7 +3298,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971016049385071</v>
+        <v>0.971016108989716</v>
       </c>
       <c r="H101" t="n">
         <v>19652</v>
@@ -3385,7 +3385,7 @@
         <v>1.11758697032928</v>
       </c>
       <c r="G104" t="n">
-        <v>0.995733380317688</v>
+        <v>0.995733320713043</v>
       </c>
       <c r="H104" t="n">
         <v>10358</v>
@@ -3443,7 +3443,7 @@
         <v>1.13443005084991</v>
       </c>
       <c r="G106" t="n">
-        <v>1.01074004173279</v>
+        <v>1.0107399225235</v>
       </c>
       <c r="H106" t="n">
         <v>17337</v>
@@ -80125,6 +80125,35 @@
         <v>0</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.939238011837006</v>
+        <v>0.939237952232361</v>
       </c>
       <c r="H3" t="n">
         <v>17307</v>
@@ -485,7 +485,7 @@
         <v>1.04030704498291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926879465579987</v>
+        <v>0.926879405975342</v>
       </c>
       <c r="H4" t="n">
         <v>6401</v>
@@ -514,7 +514,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.910106956958771</v>
+        <v>0.910106897354126</v>
       </c>
       <c r="H5" t="n">
         <v>44193</v>
@@ -601,7 +601,7 @@
         <v>1.01058399677277</v>
       </c>
       <c r="G8" t="n">
-        <v>0.900397181510925</v>
+        <v>0.900397121906281</v>
       </c>
       <c r="H8" t="n">
         <v>23254</v>
@@ -630,7 +630,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910106956958771</v>
+        <v>0.910106897354126</v>
       </c>
       <c r="H9" t="n">
         <v>24329</v>
@@ -659,7 +659,7 @@
         <v>1.02049195766449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.909224808216095</v>
+        <v>0.90922486782074</v>
       </c>
       <c r="H10" t="n">
         <v>2966</v>
@@ -688,7 +688,7 @@
         <v>0.998695015907288</v>
       </c>
       <c r="G11" t="n">
-        <v>0.889804422855377</v>
+        <v>0.889804482460022</v>
       </c>
       <c r="H11" t="n">
         <v>63536</v>
@@ -804,7 +804,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G15" t="n">
-        <v>0.882742702960968</v>
+        <v>0.882742643356323</v>
       </c>
       <c r="H15" t="n">
         <v>17895</v>
@@ -891,7 +891,7 @@
         <v>0.951138019561768</v>
       </c>
       <c r="G18" t="n">
-        <v>0.847432792186737</v>
+        <v>0.847432732582092</v>
       </c>
       <c r="H18" t="n">
         <v>8438</v>
@@ -920,7 +920,7 @@
         <v>0.970457971096039</v>
       </c>
       <c r="G19" t="n">
-        <v>0.864646255970001</v>
+        <v>0.864646196365356</v>
       </c>
       <c r="H19" t="n">
         <v>3784</v>
@@ -949,7 +949,7 @@
         <v>0.968972027301788</v>
       </c>
       <c r="G20" t="n">
-        <v>0.863322257995605</v>
+        <v>0.86332231760025</v>
       </c>
       <c r="H20" t="n">
         <v>1418</v>
@@ -1268,7 +1268,7 @@
         <v>0.790633022785187</v>
       </c>
       <c r="G31" t="n">
-        <v>0.70442807674408</v>
+        <v>0.704428136348724</v>
       </c>
       <c r="H31" t="n">
         <v>7569</v>
@@ -1558,7 +1558,7 @@
         <v>0.910516023635864</v>
       </c>
       <c r="G41" t="n">
-        <v>0.811239898204803</v>
+        <v>0.811239838600159</v>
       </c>
       <c r="H41" t="n">
         <v>26265</v>
@@ -1616,7 +1616,7 @@
         <v>0.965503990650177</v>
       </c>
       <c r="G43" t="n">
-        <v>0.860232412815094</v>
+        <v>0.860232353210449</v>
       </c>
       <c r="H43" t="n">
         <v>5234</v>
@@ -1732,7 +1732,7 @@
         <v>0.946183979511261</v>
       </c>
       <c r="G47" t="n">
-        <v>0.84301882982254</v>
+        <v>0.843018889427185</v>
       </c>
       <c r="H47" t="n">
         <v>9568</v>
@@ -1819,7 +1819,7 @@
         <v>0.924881994724274</v>
       </c>
       <c r="G50" t="n">
-        <v>0.82403951883316</v>
+        <v>0.824039459228516</v>
       </c>
       <c r="H50" t="n">
         <v>7700</v>
@@ -1848,7 +1848,7 @@
         <v>0.920423984527588</v>
       </c>
       <c r="G51" t="n">
-        <v>0.820067524909973</v>
+        <v>0.820067584514618</v>
       </c>
       <c r="H51" t="n">
         <v>5213</v>
@@ -2109,7 +2109,7 @@
         <v>0.935781002044678</v>
       </c>
       <c r="G60" t="n">
-        <v>0.833750128746033</v>
+        <v>0.833750188350677</v>
       </c>
       <c r="H60" t="n">
         <v>4464</v>
@@ -2196,7 +2196,7 @@
         <v>0.95856899023056</v>
       </c>
       <c r="G63" t="n">
-        <v>0.854053497314453</v>
+        <v>0.854053556919098</v>
       </c>
       <c r="H63" t="n">
         <v>17257</v>
@@ -2283,7 +2283,7 @@
         <v>0.952624022960663</v>
       </c>
       <c r="G66" t="n">
-        <v>0.848756730556488</v>
+        <v>0.848756670951843</v>
       </c>
       <c r="H66" t="n">
         <v>10698</v>
@@ -2312,7 +2312,7 @@
         <v>0.971943974494934</v>
       </c>
       <c r="G67" t="n">
-        <v>0.865970194339752</v>
+        <v>0.865970134735107</v>
       </c>
       <c r="H67" t="n">
         <v>10093</v>
@@ -2399,7 +2399,7 @@
         <v>0.957081973552704</v>
       </c>
       <c r="G70" t="n">
-        <v>0.852728664875031</v>
+        <v>0.852728605270386</v>
       </c>
       <c r="H70" t="n">
         <v>20319</v>
@@ -2428,7 +2428,7 @@
         <v>0.979870021343231</v>
       </c>
       <c r="G71" t="n">
-        <v>0.873031973838806</v>
+        <v>0.873032033443451</v>
       </c>
       <c r="H71" t="n">
         <v>1148</v>
@@ -2486,7 +2486,7 @@
         <v>1.01652801036835</v>
       </c>
       <c r="G73" t="n">
-        <v>0.905693113803864</v>
+        <v>0.905693054199219</v>
       </c>
       <c r="H73" t="n">
         <v>22149</v>
@@ -2515,7 +2515,7 @@
         <v>1.05814099311829</v>
       </c>
       <c r="G74" t="n">
-        <v>0.942768931388855</v>
+        <v>0.94276887178421</v>
       </c>
       <c r="H74" t="n">
         <v>43122</v>
@@ -2573,7 +2573,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G76" t="n">
-        <v>0.986905694007874</v>
+        <v>0.986905634403229</v>
       </c>
       <c r="H76" t="n">
         <v>69226</v>
@@ -2602,7 +2602,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G77" t="n">
-        <v>0.997498333454132</v>
+        <v>0.997498393058777</v>
       </c>
       <c r="H77" t="n">
         <v>75982</v>
@@ -2631,7 +2631,7 @@
         <v>1.18595004081726</v>
       </c>
       <c r="G78" t="n">
-        <v>1.05664253234863</v>
+        <v>1.05664265155792</v>
       </c>
       <c r="H78" t="n">
         <v>93047</v>
@@ -2718,7 +2718,7 @@
         <v>1.1274950504303</v>
       </c>
       <c r="G81" t="n">
-        <v>1.00456094741821</v>
+        <v>1.0045610666275</v>
       </c>
       <c r="H81" t="n">
         <v>21319</v>
@@ -2805,7 +2805,7 @@
         <v>1.19982099533081</v>
       </c>
       <c r="G84" t="n">
-        <v>1.06900119781494</v>
+        <v>1.06900107860565</v>
       </c>
       <c r="H84" t="n">
         <v>17658</v>
@@ -2834,7 +2834,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G85" t="n">
-        <v>1.08930349349976</v>
+        <v>1.08930361270905</v>
       </c>
       <c r="H85" t="n">
         <v>16563</v>
@@ -2863,7 +2863,7 @@
         <v>1.16018998622894</v>
       </c>
       <c r="G86" t="n">
-        <v>1.03369128704071</v>
+        <v>1.03369116783142</v>
       </c>
       <c r="H86" t="n">
         <v>35930</v>
@@ -2950,7 +2950,7 @@
         <v>1.13641202449799</v>
       </c>
       <c r="G89" t="n">
-        <v>1.0125058889389</v>
+        <v>1.01250576972961</v>
       </c>
       <c r="H89" t="n">
         <v>15210</v>
@@ -3037,7 +3037,7 @@
         <v>1.10767900943756</v>
       </c>
       <c r="G92" t="n">
-        <v>0.986905694007874</v>
+        <v>0.986905634403229</v>
       </c>
       <c r="H92" t="n">
         <v>21899</v>
@@ -3066,7 +3066,7 @@
         <v>1.10569798946381</v>
       </c>
       <c r="G93" t="n">
-        <v>0.98514062166214</v>
+        <v>0.985140681266785</v>
       </c>
       <c r="H93" t="n">
         <v>45101</v>
@@ -3095,7 +3095,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G94" t="n">
-        <v>0.970134019851685</v>
+        <v>0.970134079456329</v>
       </c>
       <c r="H94" t="n">
         <v>1518</v>
@@ -3124,7 +3124,7 @@
         <v>1.07795596122742</v>
       </c>
       <c r="G95" t="n">
-        <v>0.960423409938812</v>
+        <v>0.960423350334167</v>
       </c>
       <c r="H95" t="n">
         <v>45454</v>
@@ -3240,7 +3240,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G99" t="n">
-        <v>0.970134019851685</v>
+        <v>0.970134079456329</v>
       </c>
       <c r="H99" t="n">
         <v>20985</v>
@@ -3269,7 +3269,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G100" t="n">
-        <v>0.944533884525299</v>
+        <v>0.944533944129944</v>
       </c>
       <c r="H100" t="n">
         <v>12814</v>
@@ -3298,7 +3298,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971016108989716</v>
+        <v>0.971015989780426</v>
       </c>
       <c r="H101" t="n">
         <v>19652</v>
@@ -3327,7 +3327,7 @@
         <v>1.11956799030304</v>
       </c>
       <c r="G102" t="n">
-        <v>0.997498333454132</v>
+        <v>0.997498393058777</v>
       </c>
       <c r="H102" t="n">
         <v>21901</v>
@@ -3385,7 +3385,7 @@
         <v>1.11758697032928</v>
       </c>
       <c r="G104" t="n">
-        <v>0.995733320713043</v>
+        <v>0.995733201503754</v>
       </c>
       <c r="H104" t="n">
         <v>10358</v>
@@ -3588,7 +3588,7 @@
         <v>1.12947595119476</v>
       </c>
       <c r="G111" t="n">
-        <v>1.05007886886597</v>
+        <v>1.05007898807526</v>
       </c>
       <c r="H111" t="n">
         <v>19102</v>
@@ -3646,7 +3646,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G113" t="n">
-        <v>0.99296909570694</v>
+        <v>0.992969155311584</v>
       </c>
       <c r="H113" t="n">
         <v>29366</v>
@@ -3675,7 +3675,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G114" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H114" t="n">
         <v>77975</v>
@@ -3733,7 +3733,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G116" t="n">
-        <v>0.953360915184021</v>
+        <v>0.953360855579376</v>
       </c>
       <c r="H116" t="n">
         <v>15611</v>
@@ -3762,7 +3762,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G117" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H117" t="n">
         <v>9790</v>
@@ -3849,7 +3849,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G120" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H120" t="n">
         <v>8326</v>
@@ -3907,7 +3907,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G122" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H122" t="n">
         <v>4774</v>
@@ -3965,7 +3965,7 @@
         <v>0.989777982234955</v>
       </c>
       <c r="G124" t="n">
-        <v>0.920201122760773</v>
+        <v>0.920201063156128</v>
       </c>
       <c r="H124" t="n">
         <v>90762</v>
@@ -4400,7 +4400,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G139" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H139" t="n">
         <v>15649</v>
@@ -4516,7 +4516,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G143" t="n">
-        <v>0.952440440654755</v>
+        <v>0.95244038105011</v>
       </c>
       <c r="H143" t="n">
         <v>8705</v>
@@ -4545,7 +4545,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G144" t="n">
-        <v>0.944150269031525</v>
+        <v>0.944150328636169</v>
       </c>
       <c r="H144" t="n">
         <v>8451</v>
@@ -4951,7 +4951,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G158" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H158" t="n">
         <v>8684</v>
@@ -4980,7 +4980,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G159" t="n">
-        <v>0.993890345096588</v>
+        <v>0.993890404701233</v>
       </c>
       <c r="H159" t="n">
         <v>25293</v>
@@ -5067,7 +5067,7 @@
         <v>1.03931605815887</v>
       </c>
       <c r="G162" t="n">
-        <v>0.966256856918335</v>
+        <v>0.96625691652298</v>
       </c>
       <c r="H162" t="n">
         <v>4037</v>
@@ -5125,7 +5125,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G164" t="n">
-        <v>0.959809362888336</v>
+        <v>0.959809303283691</v>
       </c>
       <c r="H164" t="n">
         <v>4758</v>
@@ -5154,7 +5154,7 @@
         <v>1.02445495128632</v>
       </c>
       <c r="G165" t="n">
-        <v>0.952440440654755</v>
+        <v>0.95244038105011</v>
       </c>
       <c r="H165" t="n">
         <v>6186</v>
@@ -5241,7 +5241,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G168" t="n">
-        <v>0.993890345096588</v>
+        <v>0.993890404701233</v>
       </c>
       <c r="H168" t="n">
         <v>26716</v>
@@ -5357,7 +5357,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G172" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H172" t="n">
         <v>5069</v>
@@ -5560,7 +5560,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G179" t="n">
-        <v>0.996654331684113</v>
+        <v>0.996654391288757</v>
       </c>
       <c r="H179" t="n">
         <v>8029</v>
@@ -5618,7 +5618,7 @@
         <v>1.09876203536987</v>
       </c>
       <c r="G181" t="n">
-        <v>1.02152395248413</v>
+        <v>1.02152407169342</v>
       </c>
       <c r="H181" t="n">
         <v>18375</v>
@@ -5879,7 +5879,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G190" t="n">
-        <v>0.994811713695526</v>
+        <v>0.994811773300171</v>
       </c>
       <c r="H190" t="n">
         <v>25435</v>
@@ -5937,7 +5937,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G192" t="n">
-        <v>0.986521601676941</v>
+        <v>0.986521542072296</v>
       </c>
       <c r="H192" t="n">
         <v>2493</v>
@@ -5966,7 +5966,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G193" t="n">
-        <v>0.971783995628357</v>
+        <v>0.971783936023712</v>
       </c>
       <c r="H193" t="n">
         <v>1211</v>
@@ -5995,7 +5995,7 @@
         <v>1.06903898715973</v>
       </c>
       <c r="G194" t="n">
-        <v>0.993890345096588</v>
+        <v>0.993890404701233</v>
       </c>
       <c r="H194" t="n">
         <v>5778</v>
@@ -6169,7 +6169,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G200" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H200" t="n">
         <v>4188</v>
@@ -6227,7 +6227,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G202" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H202" t="n">
         <v>4028</v>
@@ -6256,7 +6256,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G203" t="n">
-        <v>0.96441513299942</v>
+        <v>0.964415073394775</v>
       </c>
       <c r="H203" t="n">
         <v>596</v>
@@ -6285,7 +6285,7 @@
         <v>1.03733503818512</v>
       </c>
       <c r="G204" t="n">
-        <v>0.96441513299942</v>
+        <v>0.964415073394775</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>1.04129803180695</v>
       </c>
       <c r="G205" t="n">
-        <v>0.968099474906921</v>
+        <v>0.968099534511566</v>
       </c>
       <c r="H205" t="n">
         <v>14297</v>
@@ -6343,7 +6343,7 @@
         <v>1.04526102542877</v>
       </c>
       <c r="G206" t="n">
-        <v>0.971783995628357</v>
+        <v>0.971783936023712</v>
       </c>
       <c r="H206" t="n">
         <v>1110</v>
@@ -6372,7 +6372,7 @@
         <v>1.05318701267242</v>
       </c>
       <c r="G207" t="n">
-        <v>0.979152739048004</v>
+        <v>0.979152798652649</v>
       </c>
       <c r="H207" t="n">
         <v>7791</v>
@@ -6401,7 +6401,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G208" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H208" t="n">
         <v>11810</v>
@@ -6430,7 +6430,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G209" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H209" t="n">
         <v>10194</v>
@@ -6459,7 +6459,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G210" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H210" t="n">
         <v>9285</v>
@@ -6488,7 +6488,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G211" t="n">
-        <v>0.99296909570694</v>
+        <v>0.992969155311584</v>
       </c>
       <c r="H211" t="n">
         <v>14863</v>
@@ -6517,7 +6517,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G212" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H212" t="n">
         <v>9225</v>
@@ -6546,7 +6546,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G213" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H213" t="n">
         <v>6810</v>
@@ -6604,7 +6604,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G215" t="n">
-        <v>0.980074107646942</v>
+        <v>0.980074048042297</v>
       </c>
       <c r="H215" t="n">
         <v>13653</v>
@@ -6633,7 +6633,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G216" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H216" t="n">
         <v>8511</v>
@@ -6662,7 +6662,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G217" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H217" t="n">
         <v>1379</v>
@@ -6691,7 +6691,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G218" t="n">
-        <v>0.969019830226898</v>
+        <v>0.969019889831543</v>
       </c>
       <c r="H218" t="n">
         <v>6626</v>
@@ -6720,7 +6720,7 @@
         <v>1.04228794574738</v>
       </c>
       <c r="G219" t="n">
-        <v>0.969019830226898</v>
+        <v>0.969019889831543</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.01850998401642</v>
       </c>
       <c r="G223" t="n">
-        <v>0.946913421154022</v>
+        <v>0.946913361549377</v>
       </c>
       <c r="H223" t="n">
         <v>14159</v>
@@ -6894,7 +6894,7 @@
         <v>1.01553797721863</v>
       </c>
       <c r="G225" t="n">
-        <v>0.944150269031525</v>
+        <v>0.944150328636169</v>
       </c>
       <c r="H225" t="n">
         <v>2501</v>
@@ -6952,7 +6952,7 @@
         <v>1.01256501674652</v>
       </c>
       <c r="G227" t="n">
-        <v>0.941386282444</v>
+        <v>0.941386342048645</v>
       </c>
       <c r="H227" t="n">
         <v>3071</v>
@@ -6981,7 +6981,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G228" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H228" t="n">
         <v>11372</v>
@@ -7010,7 +7010,7 @@
         <v>1.00067603588104</v>
       </c>
       <c r="G229" t="n">
-        <v>0.930333018302917</v>
+        <v>0.930333077907562</v>
       </c>
       <c r="H229" t="n">
         <v>18001</v>
@@ -7039,7 +7039,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G230" t="n">
-        <v>0.921122491359711</v>
+        <v>0.921122431755066</v>
       </c>
       <c r="H230" t="n">
         <v>8579</v>
@@ -7068,7 +7068,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G231" t="n">
-        <v>0.908226549625397</v>
+        <v>0.908226490020752</v>
       </c>
       <c r="H231" t="n">
         <v>19373</v>
@@ -7097,7 +7097,7 @@
         <v>0.976898014545441</v>
       </c>
       <c r="G232" t="n">
-        <v>0.908226549625397</v>
+        <v>0.908226490020752</v>
       </c>
       <c r="H232" t="n">
         <v>3324</v>
@@ -7155,7 +7155,7 @@
         <v>0.990769028663635</v>
       </c>
       <c r="G234" t="n">
-        <v>0.921122491359711</v>
+        <v>0.921122431755066</v>
       </c>
       <c r="H234" t="n">
         <v>17158</v>
@@ -7358,7 +7358,7 @@
         <v>1.02544498443604</v>
       </c>
       <c r="G241" t="n">
-        <v>0.953360915184021</v>
+        <v>0.953360855579376</v>
       </c>
       <c r="H241" t="n">
         <v>15341</v>
@@ -7532,7 +7532,7 @@
         <v>1.03238105773926</v>
       </c>
       <c r="G247" t="n">
-        <v>0.959809362888336</v>
+        <v>0.959809303283691</v>
       </c>
       <c r="H247" t="n">
         <v>10361</v>
@@ -7590,7 +7590,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G249" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H249" t="n">
         <v>73427</v>
@@ -7619,7 +7619,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G250" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H250" t="n">
         <v>13479</v>
@@ -7648,7 +7648,7 @@
         <v>1.05715000629425</v>
       </c>
       <c r="G251" t="n">
-        <v>0.982837200164795</v>
+        <v>0.98283714056015</v>
       </c>
       <c r="H251" t="n">
         <v>36869</v>
@@ -7677,7 +7677,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G252" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H252" t="n">
         <v>4734</v>
@@ -7706,7 +7706,7 @@
         <v>1.03634405136108</v>
       </c>
       <c r="G253" t="n">
-        <v>0.963493824005127</v>
+        <v>0.963493764400482</v>
       </c>
       <c r="H253" t="n">
         <v>12686</v>
@@ -7793,7 +7793,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G256" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H256" t="n">
         <v>2465</v>
@@ -7909,7 +7909,7 @@
         <v>1.06111299991608</v>
       </c>
       <c r="G260" t="n">
-        <v>0.986521601676941</v>
+        <v>0.986521542072296</v>
       </c>
       <c r="H260" t="n">
         <v>12963</v>
@@ -8025,7 +8025,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G264" t="n">
-        <v>0.994811713695526</v>
+        <v>0.994811773300171</v>
       </c>
       <c r="H264" t="n">
         <v>18431</v>
@@ -8199,7 +8199,7 @@
         <v>1.09182703495026</v>
       </c>
       <c r="G270" t="n">
-        <v>1.01507651805878</v>
+        <v>1.01507663726807</v>
       </c>
       <c r="H270" t="n">
         <v>5995</v>
@@ -8286,7 +8286,7 @@
         <v>1.1086699962616</v>
       </c>
       <c r="G273" t="n">
-        <v>1.0307354927063</v>
+        <v>1.03073561191559</v>
       </c>
       <c r="H273" t="n">
         <v>17630</v>
@@ -8373,7 +8373,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G276" t="n">
-        <v>0.996654331684113</v>
+        <v>0.996654391288757</v>
       </c>
       <c r="H276" t="n">
         <v>9941</v>
@@ -8460,7 +8460,7 @@
         <v>1.07201194763184</v>
       </c>
       <c r="G279" t="n">
-        <v>0.996654331684113</v>
+        <v>0.996654391288757</v>
       </c>
       <c r="H279" t="n">
         <v>504</v>
@@ -8547,7 +8547,7 @@
         <v>1.07002997398376</v>
       </c>
       <c r="G282" t="n">
-        <v>0.994811713695526</v>
+        <v>0.994811773300171</v>
       </c>
       <c r="H282" t="n">
         <v>2869</v>
@@ -8576,7 +8576,7 @@
         <v>1.0492240190506</v>
       </c>
       <c r="G283" t="n">
-        <v>0.975468277931213</v>
+        <v>0.975468397140503</v>
       </c>
       <c r="H283" t="n">
         <v>201</v>
@@ -8605,7 +8605,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G284" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H284" t="n">
         <v>19922</v>
@@ -8634,7 +8634,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G285" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H285" t="n">
         <v>6055</v>
@@ -8663,7 +8663,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G286" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H286" t="n">
         <v>4022</v>
@@ -8692,7 +8692,7 @@
         <v>1.06210398674011</v>
       </c>
       <c r="G287" t="n">
-        <v>0.987442851066589</v>
+        <v>0.987442910671234</v>
       </c>
       <c r="H287" t="n">
         <v>5271</v>
@@ -8721,7 +8721,7 @@
         <v>1.0650759935379</v>
       </c>
       <c r="G288" t="n">
-        <v>0.990206062793732</v>
+        <v>0.990205943584442</v>
       </c>
       <c r="H288" t="n">
         <v>23250</v>
@@ -8750,7 +8750,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G289" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H289" t="n">
         <v>11556</v>
@@ -8779,7 +8779,7 @@
         <v>1.05615901947021</v>
       </c>
       <c r="G290" t="n">
-        <v>0.981915831565857</v>
+        <v>0.981915891170502</v>
       </c>
       <c r="H290" t="n">
         <v>2424</v>
@@ -8808,7 +8808,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G291" t="n">
-        <v>0.985600233078003</v>
+        <v>0.985600292682648</v>
       </c>
       <c r="H291" t="n">
         <v>5183</v>
@@ -8837,7 +8837,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G292" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H292" t="n">
         <v>2704</v>
@@ -8866,7 +8866,7 @@
         <v>1.07498395442963</v>
       </c>
       <c r="G293" t="n">
-        <v>0.999417543411255</v>
+        <v>0.999417424201965</v>
       </c>
       <c r="H293" t="n">
         <v>630</v>
@@ -8953,7 +8953,7 @@
         <v>1.06804800033569</v>
       </c>
       <c r="G296" t="n">
-        <v>0.99296909570694</v>
+        <v>0.992969155311584</v>
       </c>
       <c r="H296" t="n">
         <v>413</v>
@@ -9011,7 +9011,7 @@
         <v>1.11263298988342</v>
       </c>
       <c r="G298" t="n">
-        <v>1.03441989421844</v>
+        <v>1.03442001342773</v>
       </c>
       <c r="H298" t="n">
         <v>10092</v>
@@ -9185,7 +9185,7 @@
         <v>1.21270096302032</v>
       </c>
       <c r="G304" t="n">
-        <v>1.12745368480682</v>
+        <v>1.12745356559753</v>
       </c>
       <c r="H304" t="n">
         <v>345383</v>
@@ -9272,7 +9272,7 @@
         <v>1.16613495349884</v>
       </c>
       <c r="G307" t="n">
-        <v>1.08416104316711</v>
+        <v>1.08416092395782</v>
       </c>
       <c r="H307" t="n">
         <v>147608</v>
@@ -9330,7 +9330,7 @@
         <v>1.17802405357361</v>
       </c>
       <c r="G309" t="n">
-        <v>1.09521424770355</v>
+        <v>1.09521436691284</v>
       </c>
       <c r="H309" t="n">
         <v>32265</v>
@@ -9359,7 +9359,7 @@
         <v>1.1869410276413</v>
       </c>
       <c r="G310" t="n">
-        <v>1.10350441932678</v>
+        <v>1.10350453853607</v>
       </c>
       <c r="H310" t="n">
         <v>4885</v>
@@ -9504,7 +9504,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G315" t="n">
-        <v>1.13666415214539</v>
+        <v>1.13666427135468</v>
       </c>
       <c r="H315" t="n">
         <v>59543</v>
@@ -9533,7 +9533,7 @@
         <v>1.21864497661591</v>
       </c>
       <c r="G316" t="n">
-        <v>1.13297975063324</v>
+        <v>1.13297986984253</v>
       </c>
       <c r="H316" t="n">
         <v>100407</v>
@@ -9591,7 +9591,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G318" t="n">
-        <v>1.13666415214539</v>
+        <v>1.13666427135468</v>
       </c>
       <c r="H318" t="n">
         <v>22044</v>
@@ -9736,7 +9736,7 @@
         <v>1.31673204898834</v>
       </c>
       <c r="G323" t="n">
-        <v>1.22417175769806</v>
+        <v>1.22417187690735</v>
       </c>
       <c r="H323" t="n">
         <v>194343</v>
@@ -9852,7 +9852,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G327" t="n">
-        <v>1.17995774745941</v>
+        <v>1.1799578666687</v>
       </c>
       <c r="H327" t="n">
         <v>102280</v>
@@ -9939,7 +9939,7 @@
         <v>1.29889798164368</v>
       </c>
       <c r="G330" t="n">
-        <v>1.20759129524231</v>
+        <v>1.2075914144516</v>
       </c>
       <c r="H330" t="n">
         <v>47401</v>
@@ -9968,7 +9968,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G331" t="n">
-        <v>1.16521906852722</v>
+        <v>1.16521918773651</v>
       </c>
       <c r="H331" t="n">
         <v>142707</v>
@@ -10200,7 +10200,7 @@
         <v>1.22954404354095</v>
       </c>
       <c r="G339" t="n">
-        <v>1.14311277866364</v>
+        <v>1.14311265945435</v>
       </c>
       <c r="H339" t="n">
         <v>15944</v>
@@ -10287,7 +10287,7 @@
         <v>1.19783902168274</v>
       </c>
       <c r="G342" t="n">
-        <v>1.11363637447357</v>
+        <v>1.11363649368286</v>
       </c>
       <c r="H342" t="n">
         <v>10206</v>
@@ -10316,7 +10316,7 @@
         <v>1.19585800170898</v>
       </c>
       <c r="G343" t="n">
-        <v>1.1117947101593</v>
+        <v>1.11179459095001</v>
       </c>
       <c r="H343" t="n">
         <v>48580</v>
@@ -10345,7 +10345,7 @@
         <v>1.20378398895264</v>
       </c>
       <c r="G344" t="n">
-        <v>1.1191633939743</v>
+        <v>1.11916351318359</v>
       </c>
       <c r="H344" t="n">
         <v>24146</v>
@@ -10374,7 +10374,7 @@
         <v>1.22657203674316</v>
       </c>
       <c r="G345" t="n">
-        <v>1.14034950733185</v>
+        <v>1.14034962654114</v>
       </c>
       <c r="H345" t="n">
         <v>16104</v>
@@ -10461,7 +10461,7 @@
         <v>1.25332200527191</v>
       </c>
       <c r="G348" t="n">
-        <v>1.16521906852722</v>
+        <v>1.16521918773651</v>
       </c>
       <c r="H348" t="n">
         <v>32469</v>
@@ -10519,7 +10519,7 @@
         <v>1.31375896930695</v>
       </c>
       <c r="G350" t="n">
-        <v>1.22140765190125</v>
+        <v>1.22140777111053</v>
       </c>
       <c r="H350" t="n">
         <v>171747</v>
@@ -10606,7 +10606,7 @@
         <v>1.26719295978546</v>
       </c>
       <c r="G353" t="n">
-        <v>1.17811501026154</v>
+        <v>1.17811512947083</v>
       </c>
       <c r="H353" t="n">
         <v>40097</v>
@@ -10635,7 +10635,7 @@
         <v>1.26917505264282</v>
       </c>
       <c r="G354" t="n">
-        <v>1.17995774745941</v>
+        <v>1.1799578666687</v>
       </c>
       <c r="H354" t="n">
         <v>25472</v>
@@ -10809,7 +10809,7 @@
         <v>1.35834395885468</v>
       </c>
       <c r="G360" t="n">
-        <v>1.2628585100174</v>
+        <v>1.26285862922668</v>
       </c>
       <c r="H360" t="n">
         <v>4290</v>
@@ -80154,6 +80154,35 @@
         <v>0</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CSP.MI.xlsx
+++ b/data/CSP.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.05417799949646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.939237952232361</v>
+        <v>0.939238011837006</v>
       </c>
       <c r="H3" t="n">
         <v>17307</v>
@@ -485,7 +485,7 @@
         <v>1.04030704498291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926879405975342</v>
+        <v>0.926879465579987</v>
       </c>
       <c r="H4" t="n">
         <v>6401</v>
@@ -514,7 +514,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H5" t="n">
         <v>44193</v>
@@ -630,7 +630,7 @@
         <v>1.02148199081421</v>
       </c>
       <c r="G9" t="n">
-        <v>0.910106897354126</v>
+        <v>0.910106956958771</v>
       </c>
       <c r="H9" t="n">
         <v>24329</v>
@@ -659,7 +659,7 @@
         <v>1.02049195766449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.90922486782074</v>
+        <v>0.909224808216095</v>
       </c>
       <c r="H10" t="n">
         <v>2966</v>
@@ -891,7 +891,7 @@
         <v>0.951138019561768</v>
       </c>
       <c r="G18" t="n">
-        <v>0.847432732582092</v>
+        <v>0.847432792186737</v>
       </c>
       <c r="H18" t="n">
         <v>8438</v>
@@ -1007,7 +1007,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G22" t="n">
-        <v>0.85625958442688</v>
+        <v>0.856259524822235</v>
       </c>
       <c r="H22" t="n">
         <v>10047</v>
@@ -1065,7 +1065,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G24" t="n">
-        <v>0.812122821807861</v>
+        <v>0.812122881412506</v>
       </c>
       <c r="H24" t="n">
         <v>12656</v>
@@ -1181,7 +1181,7 @@
         <v>0.824814975261688</v>
       </c>
       <c r="G28" t="n">
-        <v>0.734883069992065</v>
+        <v>0.734883010387421</v>
       </c>
       <c r="H28" t="n">
         <v>19100</v>
@@ -1268,7 +1268,7 @@
         <v>0.790633022785187</v>
       </c>
       <c r="G31" t="n">
-        <v>0.704428136348724</v>
+        <v>0.70442807674408</v>
       </c>
       <c r="H31" t="n">
         <v>7569</v>
@@ -1355,7 +1355,7 @@
         <v>0.8332359790802</v>
       </c>
       <c r="G34" t="n">
-        <v>0.742385864257812</v>
+        <v>0.742385923862457</v>
       </c>
       <c r="H34" t="n">
         <v>7451</v>
@@ -1558,7 +1558,7 @@
         <v>0.910516023635864</v>
       </c>
       <c r="G41" t="n">
-        <v>0.811239838600159</v>
+        <v>0.811239898204803</v>
       </c>
       <c r="H41" t="n">
         <v>26265</v>
@@ -1587,7 +1587,7 @@
         <v>0.931321978569031</v>
       </c>
       <c r="G42" t="n">
-        <v>0.829777359962463</v>
+        <v>0.829777300357819</v>
       </c>
       <c r="H42" t="n">
         <v>12079</v>
@@ -1616,7 +1616,7 @@
         <v>0.965503990650177</v>
       </c>
       <c r="G43" t="n">
-        <v>0.860232353210449</v>
+        <v>0.860232293605804</v>
       </c>
       <c r="H43" t="n">
         <v>5234</v>
@@ -1761,7 +1761,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G48" t="n">
-        <v>0.85625958442688</v>
+        <v>0.856259524822235</v>
       </c>
       <c r="H48" t="n">
         <v>2604</v>
@@ -1790,7 +1790,7 @@
         <v>0.925378024578094</v>
       </c>
       <c r="G49" t="n">
-        <v>0.82448148727417</v>
+        <v>0.824481427669525</v>
       </c>
       <c r="H49" t="n">
         <v>16427</v>
@@ -1877,7 +1877,7 @@
         <v>0.913488984107971</v>
       </c>
       <c r="G52" t="n">
-        <v>0.813888669013977</v>
+        <v>0.813888728618622</v>
       </c>
       <c r="H52" t="n">
         <v>9147</v>
@@ -1906,7 +1906,7 @@
         <v>0.9115070104599</v>
       </c>
       <c r="G53" t="n">
-        <v>0.812122821807861</v>
+        <v>0.812122881412506</v>
       </c>
       <c r="H53" t="n">
         <v>5228</v>
@@ -1993,7 +1993,7 @@
         <v>0.9288449883461</v>
       </c>
       <c r="G56" t="n">
-        <v>0.827570378780365</v>
+        <v>0.82757043838501</v>
       </c>
       <c r="H56" t="n">
         <v>15931</v>
@@ -2022,7 +2022,7 @@
         <v>0.931321978569031</v>
       </c>
       <c r="G57" t="n">
-        <v>0.829777359962463</v>
+        <v>0.829777300357819</v>
       </c>
       <c r="H57" t="n">
         <v>15407</v>
@@ -2196,7 +2196,7 @@
         <v>0.95856899023056</v>
       </c>
       <c r="G63" t="n">
-        <v>0.854053556919098</v>
+        <v>0.854053497314453</v>
       </c>
       <c r="H63" t="n">
         <v>17257</v>
@@ -2254,7 +2254,7 @@
         <v>0.961045026779175</v>
       </c>
       <c r="G65" t="n">
-        <v>0.85625958442688</v>
+        <v>0.856259524822235</v>
       </c>
       <c r="H65" t="n">
         <v>25879</v>
@@ -2283,7 +2283,7 @@
         <v>0.952624022960663</v>
       </c>
       <c r="G66" t="n">
-        <v>0.848756670951843</v>
+        <v>0.848756730556488</v>
       </c>
       <c r="H66" t="n">
         <v>10698</v>
@@ -2399,7 +2399,7 @@
         <v>0.957081973552704</v>
       </c>
       <c r="G70" t="n">
-        <v>0.852728605270386</v>
+        <v>0.852728664875031</v>
       </c>
       <c r="H70" t="n">
         <v>20319</v>
@@ -2544,7 +2544,7 @@
         <v>1.0710209608078</v>
       </c>
       <c r="G75" t="n">
-        <v>0.954244554042816</v>
+        <v>0.954244494438171</v>
       </c>
       <c r="H75" t="n">
         <v>62338</v>
@@ -2776,7 +2776,7 @@
         <v>1.19387602806091</v>
       </c>
       <c r="G83" t="n">
-        <v>1.06370437145233</v>
+        <v>1.06370425224304</v>
       </c>
       <c r="H83" t="n">
         <v>21496</v>
@@ -2805,7 +2805,7 @@
         <v>1.19982099533081</v>
       </c>
       <c r="G84" t="n">
-        <v>1.06900107860565</v>
+        <v>1.06900119781494</v>
       </c>
       <c r="H84" t="n">
         <v>17658</v>
@@ -2834,7 +2834,7 @@
         <v>1.22260797023773</v>
       </c>
       <c r="G85" t="n">
-        <v>1.08930361270905</v>
+        <v>1.08930349349976</v>
       </c>
       <c r="H85" t="n">
         <v>16563</v>
@@ -2921,7 +2921,7 @@
         <v>1.13938403129578</v>
       </c>
       <c r="G88" t="n">
-        <v>1.01515376567841</v>
+        <v>1.0151538848877</v>
       </c>
       <c r="H88" t="n">
         <v>43542</v>
@@ -3095,7 +3095,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G94" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134198665619</v>
       </c>
       <c r="H94" t="n">
         <v>1518</v>
@@ -3240,7 +3240,7 @@
         <v>1.08885502815247</v>
       </c>
       <c r="G99" t="n">
-        <v>0.970134079456329</v>
+        <v>0.970134198665619</v>
       </c>
       <c r="H99" t="n">
         <v>20985</v>
@@ -3269,7 +3269,7 @@
         <v>1.06012201309204</v>
       </c>
       <c r="G100" t="n">
-        <v>0.944533944129944</v>
+        <v>0.944534003734589</v>
       </c>
       <c r="H100" t="n">
         <v>12814</v>
@@ -3298,7 +3298,7 @@
         <v>1.0898449420929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.971015989780426</v>
+        <v>0.971016108989716</v>
       </c>
       <c r="H101" t="n">
         <v>19652</v>
@@ -80183,6 +80183,64 @@
         <v>0</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.264999985694885</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>0.273999989032745</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>0.275000005960464</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>0.273999989032745</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>0.275000005960464</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>0.275000005960464</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>10091</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
